--- a/Emp_ List-Updated.xlsx
+++ b/Emp_ List-Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohamedShakeel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AB702E-DD42-4A73-AFDC-2C25AD6C4FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2170CC85-25B8-4EBF-A68B-C379E53D3A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D210C182-0804-46D5-AC5E-017469378BAD}"/>
   </bookViews>
@@ -4016,7 +4016,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4120,9 +4120,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="15" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -4188,11 +4185,17 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4560,13 +4563,13 @@
     <col min="5" max="5" width="30.42578125" customWidth="1"/>
     <col min="6" max="6" width="31.5703125" customWidth="1"/>
     <col min="7" max="8" width="8.5703125" customWidth="1"/>
-    <col min="9" max="10" width="19" style="46" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="19" style="45" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" style="61" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="13.5703125" customWidth="1"/>
     <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="28.85546875" style="44" customWidth="1"/>
+    <col min="15" max="15" width="28.85546875" style="43" customWidth="1"/>
     <col min="16" max="16" width="19.5703125" customWidth="1"/>
-    <col min="17" max="17" width="36" style="44" customWidth="1"/>
+    <col min="17" max="17" width="36" style="43" customWidth="1"/>
     <col min="18" max="18" width="14.28515625" customWidth="1"/>
     <col min="19" max="19" width="39.140625" customWidth="1"/>
     <col min="20" max="20" width="4.5703125" style="13" customWidth="1"/>
@@ -4598,13 +4601,13 @@
       <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="44" t="s">
         <v>929</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="59" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -4634,56 +4637,56 @@
       <c r="T3" s="2"/>
     </row>
     <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47">
+      <c r="A4" s="46">
         <v>93436</v>
       </c>
-      <c r="B4" s="47">
+      <c r="B4" s="46">
         <v>693</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="47" t="s">
         <v>802</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="46" t="s">
         <v>803</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="46" t="s">
         <v>803</v>
       </c>
-      <c r="G4" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="47" t="s">
+      <c r="G4" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="46" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="J4" s="59" t="s">
+      <c r="J4" s="5" t="s">
         <v>930</v>
       </c>
-      <c r="K4" s="60">
+      <c r="K4" s="58">
         <f ca="1">(TODAY()-(DATEVALUE(SUBSTITUTE(J4,".","/"))))/(365)</f>
         <v>39.860273972602741</v>
       </c>
-      <c r="L4" s="49" t="s">
+      <c r="L4" s="48" t="s">
         <v>804</v>
       </c>
-      <c r="M4" s="47">
+      <c r="M4" s="46">
         <v>28652453480</v>
       </c>
-      <c r="N4" s="47" t="s">
+      <c r="N4" s="46" t="s">
         <v>805</v>
       </c>
-      <c r="O4" s="51" t="s">
+      <c r="O4" s="50" t="s">
         <v>927</v>
       </c>
-      <c r="P4" s="47">
+      <c r="P4" s="46">
         <v>97466758168</v>
       </c>
-      <c r="Q4" s="47" t="s">
+      <c r="Q4" s="46" t="s">
         <v>806</v>
       </c>
       <c r="R4" s="4" t="s">
@@ -4692,7 +4695,7 @@
       <c r="S4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="U4" s="58"/>
+      <c r="U4" s="57"/>
     </row>
     <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
@@ -4722,10 +4725,10 @@
       <c r="I5" s="8" t="s">
         <v>1125</v>
       </c>
-      <c r="J5" s="59" t="s">
+      <c r="J5" s="5" t="s">
         <v>931</v>
       </c>
-      <c r="K5" s="60">
+      <c r="K5" s="58">
         <f ca="1">(TODAY()-(DATEVALUE(SUBSTITUTE(J5,".","/"))))/(365)</f>
         <v>54.142465753424659</v>
       </c>
@@ -4783,10 +4786,10 @@
       <c r="I6" s="8" t="s">
         <v>1126</v>
       </c>
-      <c r="J6" s="59" t="s">
+      <c r="J6" s="5" t="s">
         <v>932</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="58">
         <f t="shared" ref="K6:K69" ca="1" si="0">(TODAY()-(DATEVALUE(SUBSTITUTE(J6,".","/"))))/(365)</f>
         <v>53.747945205479454</v>
       </c>
@@ -4816,56 +4819,56 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="47">
+      <c r="A7" s="46">
         <v>93430</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="46">
         <v>687</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="47" t="s">
         <v>773</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="46" t="s">
         <v>605</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="46" t="s">
         <v>774</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="46" t="s">
         <v>775</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="46" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>1127</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="5" t="s">
         <v>933</v>
       </c>
-      <c r="K7" s="60">
+      <c r="K7" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>33.315068493150683</v>
       </c>
-      <c r="L7" s="47">
+      <c r="L7" s="46">
         <v>42926</v>
       </c>
-      <c r="M7" s="47">
+      <c r="M7" s="46">
         <v>29235636492</v>
       </c>
-      <c r="N7" s="47" t="s">
+      <c r="N7" s="46" t="s">
         <v>776</v>
       </c>
-      <c r="O7" s="51" t="s">
+      <c r="O7" s="50" t="s">
         <v>168</v>
       </c>
-      <c r="P7" s="47" t="s">
+      <c r="P7" s="46" t="s">
         <v>777</v>
       </c>
-      <c r="Q7" s="47" t="s">
+      <c r="Q7" s="46" t="s">
         <v>778</v>
       </c>
       <c r="R7" s="4" t="s">
@@ -4904,10 +4907,10 @@
       <c r="I8" s="8" t="s">
         <v>1128</v>
       </c>
-      <c r="J8" s="59" t="s">
+      <c r="J8" s="5" t="s">
         <v>934</v>
       </c>
-      <c r="K8" s="60">
+      <c r="K8" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>49.586301369863016</v>
       </c>
@@ -4964,10 +4967,10 @@
       <c r="I9" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="J9" s="59" t="s">
+      <c r="J9" s="5" t="s">
         <v>935</v>
       </c>
-      <c r="K9" s="60">
+      <c r="K9" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>40.273972602739725</v>
       </c>
@@ -5024,10 +5027,10 @@
       <c r="I10" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="J10" s="59" t="s">
+      <c r="J10" s="5" t="s">
         <v>936</v>
       </c>
-      <c r="K10" s="60">
+      <c r="K10" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>62.975342465753428</v>
       </c>
@@ -5084,10 +5087,10 @@
       <c r="I11" s="8" t="s">
         <v>1131</v>
       </c>
-      <c r="J11" s="59" t="s">
+      <c r="J11" s="5" t="s">
         <v>937</v>
       </c>
-      <c r="K11" s="60">
+      <c r="K11" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>30.172602739726027</v>
       </c>
@@ -5144,10 +5147,10 @@
       <c r="I12" s="8" t="s">
         <v>1132</v>
       </c>
-      <c r="J12" s="59" t="s">
+      <c r="J12" s="5" t="s">
         <v>938</v>
       </c>
-      <c r="K12" s="60">
+      <c r="K12" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>28.898630136986302</v>
       </c>
@@ -5204,10 +5207,10 @@
       <c r="I13" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="J13" s="59" t="s">
+      <c r="J13" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="K13" s="60">
+      <c r="K13" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>50.172602739726024</v>
       </c>
@@ -5264,10 +5267,10 @@
       <c r="I14" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J14" s="59" t="s">
+      <c r="J14" s="5" t="s">
         <v>940</v>
       </c>
-      <c r="K14" s="60">
+      <c r="K14" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>45.57260273972603</v>
       </c>
@@ -5324,10 +5327,10 @@
       <c r="I15" s="8" t="s">
         <v>1135</v>
       </c>
-      <c r="J15" s="59" t="s">
+      <c r="J15" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="K15" s="60">
+      <c r="K15" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>61.835616438356162</v>
       </c>
@@ -5385,10 +5388,10 @@
       <c r="I16" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J16" s="59" t="s">
+      <c r="J16" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="K16" s="60">
+      <c r="K16" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>46.246575342465754</v>
       </c>
@@ -5445,10 +5448,10 @@
       <c r="I17" s="8" t="s">
         <v>1136</v>
       </c>
-      <c r="J17" s="59" t="s">
+      <c r="J17" s="5" t="s">
         <v>943</v>
       </c>
-      <c r="K17" s="60">
+      <c r="K17" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>33.194520547945203</v>
       </c>
@@ -5505,10 +5508,10 @@
       <c r="I18" s="8" t="s">
         <v>1137</v>
       </c>
-      <c r="J18" s="59" t="s">
+      <c r="J18" s="5" t="s">
         <v>944</v>
       </c>
-      <c r="K18" s="60">
+      <c r="K18" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>57.624657534246573</v>
       </c>
@@ -5565,10 +5568,10 @@
       <c r="I19" s="8" t="s">
         <v>1138</v>
       </c>
-      <c r="J19" s="59" t="s">
+      <c r="J19" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="K19" s="60">
+      <c r="K19" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>41.164383561643838</v>
       </c>
@@ -5625,10 +5628,10 @@
       <c r="I20" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J20" s="59" t="s">
+      <c r="J20" s="5" t="s">
         <v>946</v>
       </c>
-      <c r="K20" s="60">
+      <c r="K20" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>32.104109589041094</v>
       </c>
@@ -5658,56 +5661,56 @@
       </c>
     </row>
     <row r="21" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47">
+      <c r="A21" s="46">
         <v>93431</v>
       </c>
-      <c r="B21" s="47">
+      <c r="B21" s="46">
         <v>688</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="47" t="s">
         <v>779</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="E21" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F21" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="G21" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="47" t="s">
+      <c r="G21" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="46" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="J21" s="59" t="s">
+      <c r="J21" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="K21" s="60">
+      <c r="K21" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>43.19178082191781</v>
       </c>
-      <c r="L21" s="47">
+      <c r="L21" s="46">
         <v>42927</v>
       </c>
-      <c r="M21" s="47">
+      <c r="M21" s="46">
         <v>28235656464</v>
       </c>
-      <c r="N21" s="47" t="s">
+      <c r="N21" s="46" t="s">
         <v>780</v>
       </c>
-      <c r="O21" s="51" t="s">
+      <c r="O21" s="50" t="s">
         <v>168</v>
       </c>
-      <c r="P21" s="47" t="s">
+      <c r="P21" s="46" t="s">
         <v>781</v>
       </c>
-      <c r="Q21" s="47" t="s">
+      <c r="Q21" s="46" t="s">
         <v>782</v>
       </c>
       <c r="R21" s="4" t="s">
@@ -5745,10 +5748,10 @@
       <c r="I22" s="8" t="s">
         <v>1140</v>
       </c>
-      <c r="J22" s="59" t="s">
+      <c r="J22" s="5" t="s">
         <v>948</v>
       </c>
-      <c r="K22" s="60">
+      <c r="K22" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>52.904109589041099</v>
       </c>
@@ -5805,10 +5808,10 @@
       <c r="I23" s="8" t="s">
         <v>1141</v>
       </c>
-      <c r="J23" s="59" t="s">
+      <c r="J23" s="5" t="s">
         <v>949</v>
       </c>
-      <c r="K23" s="60">
+      <c r="K23" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>44.835616438356162</v>
       </c>
@@ -5838,56 +5841,56 @@
       </c>
     </row>
     <row r="24" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="47">
+      <c r="A24" s="46">
         <v>93433</v>
       </c>
-      <c r="B24" s="47">
+      <c r="B24" s="46">
         <v>690</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="47" t="s">
         <v>788</v>
       </c>
-      <c r="D24" s="47" t="s">
+      <c r="D24" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="47" t="s">
+      <c r="E24" s="46" t="s">
         <v>789</v>
       </c>
-      <c r="F24" s="47" t="s">
+      <c r="F24" s="46" t="s">
         <v>789</v>
       </c>
-      <c r="G24" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" s="47" t="s">
+      <c r="G24" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="46" t="s">
         <v>23</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>1142</v>
       </c>
-      <c r="J24" s="59" t="s">
+      <c r="J24" s="5" t="s">
         <v>950</v>
       </c>
-      <c r="K24" s="60">
+      <c r="K24" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>40.131506849315066</v>
       </c>
-      <c r="L24" s="47">
+      <c r="L24" s="46">
         <v>41999</v>
       </c>
-      <c r="M24" s="47">
+      <c r="M24" s="46">
         <v>28605026382</v>
       </c>
-      <c r="N24" s="47" t="s">
+      <c r="N24" s="46" t="s">
         <v>790</v>
       </c>
-      <c r="O24" s="51" t="s">
+      <c r="O24" s="50" t="s">
         <v>927</v>
       </c>
-      <c r="P24" s="47" t="s">
+      <c r="P24" s="46" t="s">
         <v>791</v>
       </c>
-      <c r="Q24" s="47" t="s">
+      <c r="Q24" s="46" t="s">
         <v>792</v>
       </c>
       <c r="R24" s="4" t="s">
@@ -5925,10 +5928,10 @@
       <c r="I25" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="J25" s="59" t="s">
+      <c r="J25" s="5" t="s">
         <v>951</v>
       </c>
-      <c r="K25" s="60">
+      <c r="K25" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>35.860273972602741</v>
       </c>
@@ -5986,10 +5989,10 @@
       <c r="I26" s="8" t="s">
         <v>1144</v>
       </c>
-      <c r="J26" s="59" t="s">
+      <c r="J26" s="5" t="s">
         <v>952</v>
       </c>
-      <c r="K26" s="60">
+      <c r="K26" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>53.827397260273976</v>
       </c>
@@ -6046,10 +6049,10 @@
       <c r="I27" s="8" t="s">
         <v>1145</v>
       </c>
-      <c r="J27" s="59" t="s">
+      <c r="J27" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="K27" s="60">
+      <c r="K27" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>30.731506849315068</v>
       </c>
@@ -6106,10 +6109,10 @@
       <c r="I28" s="8" t="s">
         <v>1146</v>
       </c>
-      <c r="J28" s="59" t="s">
+      <c r="J28" s="5" t="s">
         <v>954</v>
       </c>
-      <c r="K28" s="60">
+      <c r="K28" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>34.857534246575341</v>
       </c>
@@ -6166,10 +6169,10 @@
       <c r="I29" s="8" t="s">
         <v>1147</v>
       </c>
-      <c r="J29" s="59" t="s">
+      <c r="J29" s="5" t="s">
         <v>955</v>
       </c>
-      <c r="K29" s="60">
+      <c r="K29" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>59.865753424657534</v>
       </c>
@@ -6199,56 +6202,56 @@
       </c>
     </row>
     <row r="30" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47">
+      <c r="A30" s="46">
         <v>93435</v>
       </c>
-      <c r="B30" s="47">
+      <c r="B30" s="46">
         <v>692</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="47" t="s">
         <v>798</v>
       </c>
-      <c r="D30" s="47" t="s">
+      <c r="D30" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="47" t="s">
+      <c r="E30" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="47" t="s">
+      <c r="F30" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="47" t="s">
+      <c r="G30" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="46" t="s">
         <v>23</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>1148</v>
       </c>
-      <c r="J30" s="59" t="s">
+      <c r="J30" s="5" t="s">
         <v>956</v>
       </c>
-      <c r="K30" s="60">
+      <c r="K30" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>24.687671232876713</v>
       </c>
-      <c r="L30" s="47">
+      <c r="L30" s="46">
         <v>42928</v>
       </c>
-      <c r="M30" s="47">
+      <c r="M30" s="46">
         <v>30135610240</v>
       </c>
-      <c r="N30" s="47" t="s">
+      <c r="N30" s="46" t="s">
         <v>799</v>
       </c>
-      <c r="O30" s="51" t="s">
+      <c r="O30" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="P30" s="47" t="s">
+      <c r="P30" s="46" t="s">
         <v>800</v>
       </c>
-      <c r="Q30" s="55" t="s">
+      <c r="Q30" s="54" t="s">
         <v>801</v>
       </c>
       <c r="R30" s="4" t="s">
@@ -6287,10 +6290,10 @@
       <c r="I31" s="8" t="s">
         <v>1149</v>
       </c>
-      <c r="J31" s="59" t="s">
+      <c r="J31" s="5" t="s">
         <v>957</v>
       </c>
-      <c r="K31" s="60">
+      <c r="K31" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>49.07123287671233</v>
       </c>
@@ -6347,10 +6350,10 @@
       <c r="I32" s="8" t="s">
         <v>1150</v>
       </c>
-      <c r="J32" s="59" t="s">
+      <c r="J32" s="5" t="s">
         <v>958</v>
       </c>
-      <c r="K32" s="60">
+      <c r="K32" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>43.846575342465755</v>
       </c>
@@ -6407,10 +6410,10 @@
       <c r="I33" s="8" t="s">
         <v>1151</v>
       </c>
-      <c r="J33" s="59" t="s">
+      <c r="J33" s="5" t="s">
         <v>959</v>
       </c>
-      <c r="K33" s="60">
+      <c r="K33" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>40.838356164383562</v>
       </c>
@@ -6467,10 +6470,10 @@
       <c r="I34" s="8" t="s">
         <v>1152</v>
       </c>
-      <c r="J34" s="59" t="s">
+      <c r="J34" s="5" t="s">
         <v>960</v>
       </c>
-      <c r="K34" s="60">
+      <c r="K34" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>39.38356164383562</v>
       </c>
@@ -6527,10 +6530,10 @@
       <c r="I35" s="8" t="s">
         <v>1153</v>
       </c>
-      <c r="J35" s="59" t="s">
+      <c r="J35" s="5" t="s">
         <v>961</v>
       </c>
-      <c r="K35" s="60">
+      <c r="K35" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>45.994520547945207</v>
       </c>
@@ -6587,10 +6590,10 @@
       <c r="I36" s="8" t="s">
         <v>1154</v>
       </c>
-      <c r="J36" s="59" t="s">
+      <c r="J36" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="K36" s="60">
+      <c r="K36" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>33.405479452054792</v>
       </c>
@@ -6648,10 +6651,10 @@
       <c r="I37" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="J37" s="59" t="s">
+      <c r="J37" s="5" t="s">
         <v>963</v>
       </c>
-      <c r="K37" s="60">
+      <c r="K37" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>38.164383561643838</v>
       </c>
@@ -6708,10 +6711,10 @@
       <c r="I38" s="8" t="s">
         <v>1155</v>
       </c>
-      <c r="J38" s="59" t="s">
+      <c r="J38" s="5" t="s">
         <v>964</v>
       </c>
-      <c r="K38" s="60">
+      <c r="K38" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>49.80821917808219</v>
       </c>
@@ -6768,10 +6771,10 @@
       <c r="I39" s="8" t="s">
         <v>1156</v>
       </c>
-      <c r="J39" s="59" t="s">
+      <c r="J39" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="K39" s="60">
+      <c r="K39" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>40.753424657534246</v>
       </c>
@@ -6828,10 +6831,10 @@
       <c r="I40" s="8" t="s">
         <v>1157</v>
       </c>
-      <c r="J40" s="59" t="s">
+      <c r="J40" s="5" t="s">
         <v>966</v>
       </c>
-      <c r="K40" s="60">
+      <c r="K40" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>45.421917808219177</v>
       </c>
@@ -6888,10 +6891,10 @@
       <c r="I41" s="8" t="s">
         <v>1158</v>
       </c>
-      <c r="J41" s="59" t="s">
+      <c r="J41" s="5" t="s">
         <v>967</v>
       </c>
-      <c r="K41" s="60">
+      <c r="K41" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>45.098630136986301</v>
       </c>
@@ -6948,10 +6951,10 @@
       <c r="I42" s="8" t="s">
         <v>1159</v>
       </c>
-      <c r="J42" s="59" t="s">
+      <c r="J42" s="5" t="s">
         <v>968</v>
       </c>
-      <c r="K42" s="60">
+      <c r="K42" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>47.81095890410959</v>
       </c>
@@ -7008,10 +7011,10 @@
       <c r="I43" s="8" t="s">
         <v>1160</v>
       </c>
-      <c r="J43" s="59" t="s">
+      <c r="J43" s="5" t="s">
         <v>969</v>
       </c>
-      <c r="K43" s="60">
+      <c r="K43" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>46.849315068493148</v>
       </c>
@@ -7068,10 +7071,10 @@
       <c r="I44" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="J44" s="59" t="s">
+      <c r="J44" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="K44" s="60">
+      <c r="K44" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>48.156164383561645</v>
       </c>
@@ -7128,10 +7131,10 @@
       <c r="I45" s="8" t="s">
         <v>1161</v>
       </c>
-      <c r="J45" s="59" t="s">
+      <c r="J45" s="5" t="s">
         <v>971</v>
       </c>
-      <c r="K45" s="60">
+      <c r="K45" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>28.484931506849314</v>
       </c>
@@ -7188,10 +7191,10 @@
       <c r="I46" s="8" t="s">
         <v>1162</v>
       </c>
-      <c r="J46" s="59" t="s">
+      <c r="J46" s="5" t="s">
         <v>972</v>
       </c>
-      <c r="K46" s="60">
+      <c r="K46" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>29.580821917808219</v>
       </c>
@@ -7210,7 +7213,7 @@
       <c r="P46" s="14" t="s">
         <v>642</v>
       </c>
-      <c r="Q46" s="56" t="s">
+      <c r="Q46" s="55" t="s">
         <v>643</v>
       </c>
       <c r="R46" s="18" t="s">
@@ -7248,10 +7251,10 @@
       <c r="I47" s="8" t="s">
         <v>1163</v>
       </c>
-      <c r="J47" s="59" t="s">
+      <c r="J47" s="5" t="s">
         <v>973</v>
       </c>
-      <c r="K47" s="60">
+      <c r="K47" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>46.397260273972606</v>
       </c>
@@ -7308,10 +7311,10 @@
       <c r="I48" s="8" t="s">
         <v>1164</v>
       </c>
-      <c r="J48" s="59" t="s">
+      <c r="J48" s="5" t="s">
         <v>974</v>
       </c>
-      <c r="K48" s="60">
+      <c r="K48" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>38.61917808219178</v>
       </c>
@@ -7368,10 +7371,10 @@
       <c r="I49" s="8" t="s">
         <v>1165</v>
       </c>
-      <c r="J49" s="59" t="s">
+      <c r="J49" s="5" t="s">
         <v>975</v>
       </c>
-      <c r="K49" s="60">
+      <c r="K49" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>54.268493150684932</v>
       </c>
@@ -7428,10 +7431,10 @@
       <c r="I50" s="8" t="s">
         <v>1166</v>
       </c>
-      <c r="J50" s="59" t="s">
+      <c r="J50" s="5" t="s">
         <v>976</v>
       </c>
-      <c r="K50" s="60">
+      <c r="K50" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>47.783561643835618</v>
       </c>
@@ -7489,10 +7492,10 @@
       <c r="I51" s="8" t="s">
         <v>1167</v>
       </c>
-      <c r="J51" s="59" t="s">
+      <c r="J51" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="K51" s="60">
+      <c r="K51" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>46.909589041095892</v>
       </c>
@@ -7549,10 +7552,10 @@
       <c r="I52" s="8" t="s">
         <v>1168</v>
       </c>
-      <c r="J52" s="59" t="s">
+      <c r="J52" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="K52" s="60">
+      <c r="K52" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>48.057534246575344</v>
       </c>
@@ -7609,10 +7612,10 @@
       <c r="I53" s="8" t="s">
         <v>1169</v>
       </c>
-      <c r="J53" s="59" t="s">
+      <c r="J53" s="5" t="s">
         <v>979</v>
       </c>
-      <c r="K53" s="60">
+      <c r="K53" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>39.821917808219176</v>
       </c>
@@ -7669,10 +7672,10 @@
       <c r="I54" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="J54" s="59" t="s">
+      <c r="J54" s="5" t="s">
         <v>980</v>
       </c>
-      <c r="K54" s="60">
+      <c r="K54" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>26.698630136986303</v>
       </c>
@@ -7729,10 +7732,10 @@
       <c r="I55" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J55" s="59" t="s">
+      <c r="J55" s="5" t="s">
         <v>981</v>
       </c>
-      <c r="K55" s="60">
+      <c r="K55" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>39.547945205479451</v>
       </c>
@@ -7789,10 +7792,10 @@
       <c r="I56" s="8" t="s">
         <v>1171</v>
       </c>
-      <c r="J56" s="59" t="s">
+      <c r="J56" s="5" t="s">
         <v>982</v>
       </c>
-      <c r="K56" s="60">
+      <c r="K56" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>49.219178082191782</v>
       </c>
@@ -7849,10 +7852,10 @@
       <c r="I57" s="8" t="s">
         <v>1172</v>
       </c>
-      <c r="J57" s="59" t="s">
+      <c r="J57" s="5" t="s">
         <v>983</v>
       </c>
-      <c r="K57" s="60">
+      <c r="K57" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>45.052054794520551</v>
       </c>
@@ -7909,10 +7912,10 @@
       <c r="I58" s="8" t="s">
         <v>1173</v>
       </c>
-      <c r="J58" s="59" t="s">
+      <c r="J58" s="5" t="s">
         <v>984</v>
       </c>
-      <c r="K58" s="60">
+      <c r="K58" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>56.969863013698628</v>
       </c>
@@ -7969,10 +7972,10 @@
       <c r="I59" s="8" t="s">
         <v>1131</v>
       </c>
-      <c r="J59" s="59" t="s">
+      <c r="J59" s="5" t="s">
         <v>985</v>
       </c>
-      <c r="K59" s="60">
+      <c r="K59" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>33.11780821917808</v>
       </c>
@@ -8029,10 +8032,10 @@
       <c r="I60" s="8" t="s">
         <v>1174</v>
       </c>
-      <c r="J60" s="59" t="s">
+      <c r="J60" s="5" t="s">
         <v>986</v>
       </c>
-      <c r="K60" s="60">
+      <c r="K60" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>47.021917808219179</v>
       </c>
@@ -8089,10 +8092,10 @@
       <c r="I61" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="J61" s="59" t="s">
+      <c r="J61" s="5" t="s">
         <v>987</v>
       </c>
-      <c r="K61" s="60">
+      <c r="K61" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>46.161643835616438</v>
       </c>
@@ -8149,10 +8152,10 @@
       <c r="I62" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J62" s="59" t="s">
+      <c r="J62" s="5" t="s">
         <v>988</v>
       </c>
-      <c r="K62" s="60">
+      <c r="K62" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>33.994520547945207</v>
       </c>
@@ -8209,10 +8212,10 @@
       <c r="I63" s="8" t="s">
         <v>1176</v>
       </c>
-      <c r="J63" s="59" t="s">
+      <c r="J63" s="5" t="s">
         <v>989</v>
       </c>
-      <c r="K63" s="60">
+      <c r="K63" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>45.016438356164386</v>
       </c>
@@ -8269,10 +8272,10 @@
       <c r="I64" s="8" t="s">
         <v>1174</v>
       </c>
-      <c r="J64" s="59" t="s">
+      <c r="J64" s="5" t="s">
         <v>990</v>
       </c>
-      <c r="K64" s="60">
+      <c r="K64" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>27.463013698630139</v>
       </c>
@@ -8302,56 +8305,56 @@
       </c>
     </row>
     <row r="65" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="47">
+      <c r="A65" s="46">
         <v>93432</v>
       </c>
-      <c r="B65" s="47">
+      <c r="B65" s="46">
         <v>689</v>
       </c>
-      <c r="C65" s="48" t="s">
+      <c r="C65" s="47" t="s">
         <v>783</v>
       </c>
-      <c r="D65" s="47" t="s">
+      <c r="D65" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="E65" s="47" t="s">
+      <c r="E65" s="46" t="s">
         <v>784</v>
       </c>
-      <c r="F65" s="47" t="s">
+      <c r="F65" s="46" t="s">
         <v>784</v>
       </c>
-      <c r="G65" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H65" s="47" t="s">
+      <c r="G65" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" s="46" t="s">
         <v>23</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>1177</v>
       </c>
-      <c r="J65" s="59" t="s">
+      <c r="J65" s="5" t="s">
         <v>991</v>
       </c>
-      <c r="K65" s="60">
+      <c r="K65" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>28.534246575342465</v>
       </c>
-      <c r="L65" s="47">
+      <c r="L65" s="46">
         <v>41998</v>
       </c>
-      <c r="M65" s="47">
+      <c r="M65" s="46">
         <v>29735634560</v>
       </c>
-      <c r="N65" s="47" t="s">
+      <c r="N65" s="46" t="s">
         <v>785</v>
       </c>
-      <c r="O65" s="51" t="s">
+      <c r="O65" s="50" t="s">
         <v>927</v>
       </c>
-      <c r="P65" s="47" t="s">
+      <c r="P65" s="46" t="s">
         <v>786</v>
       </c>
-      <c r="Q65" s="47" t="s">
+      <c r="Q65" s="46" t="s">
         <v>787</v>
       </c>
       <c r="R65" s="4" t="s">
@@ -8363,56 +8366,56 @@
       <c r="T65" s="19"/>
     </row>
     <row r="66" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="47">
+      <c r="A66" s="46">
         <v>93429</v>
       </c>
-      <c r="B66" s="47">
+      <c r="B66" s="46">
         <v>686</v>
       </c>
-      <c r="C66" s="48" t="s">
+      <c r="C66" s="47" t="s">
         <v>767</v>
       </c>
-      <c r="D66" s="47" t="s">
+      <c r="D66" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="E66" s="47" t="s">
+      <c r="E66" s="46" t="s">
         <v>768</v>
       </c>
-      <c r="F66" s="47" t="s">
+      <c r="F66" s="46" t="s">
         <v>769</v>
       </c>
-      <c r="G66" s="47" t="s">
+      <c r="G66" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="H66" s="47" t="s">
+      <c r="H66" s="46" t="s">
         <v>47</v>
       </c>
       <c r="I66" s="8" t="s">
         <v>1178</v>
       </c>
-      <c r="J66" s="59" t="s">
+      <c r="J66" s="5" t="s">
         <v>992</v>
       </c>
-      <c r="K66" s="60">
+      <c r="K66" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>40.287671232876711</v>
       </c>
-      <c r="L66" s="47">
+      <c r="L66" s="46">
         <v>23022</v>
       </c>
-      <c r="M66" s="47">
+      <c r="M66" s="46">
         <v>28552456106</v>
       </c>
-      <c r="N66" s="47" t="s">
+      <c r="N66" s="46" t="s">
         <v>770</v>
       </c>
-      <c r="O66" s="51" t="s">
+      <c r="O66" s="50" t="s">
         <v>927</v>
       </c>
-      <c r="P66" s="47" t="s">
+      <c r="P66" s="46" t="s">
         <v>771</v>
       </c>
-      <c r="Q66" s="47" t="s">
+      <c r="Q66" s="46" t="s">
         <v>772</v>
       </c>
       <c r="R66" s="4" t="s">
@@ -8451,10 +8454,10 @@
       <c r="I67" s="8" t="s">
         <v>1179</v>
       </c>
-      <c r="J67" s="59" t="s">
+      <c r="J67" s="5" t="s">
         <v>993</v>
       </c>
-      <c r="K67" s="60">
+      <c r="K67" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>56.369863013698627</v>
       </c>
@@ -8484,56 +8487,56 @@
       </c>
     </row>
     <row r="68" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="47">
+      <c r="A68" s="46">
         <v>93426</v>
       </c>
-      <c r="B68" s="47">
+      <c r="B68" s="46">
         <v>684</v>
       </c>
-      <c r="C68" s="48" t="s">
+      <c r="C68" s="47" t="s">
         <v>758</v>
       </c>
-      <c r="D68" s="47" t="s">
+      <c r="D68" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="E68" s="47" t="s">
+      <c r="E68" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="F68" s="47" t="s">
+      <c r="F68" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="G68" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H68" s="47" t="s">
+      <c r="G68" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" s="46" t="s">
         <v>23</v>
       </c>
       <c r="I68" s="8" t="s">
         <v>1180</v>
       </c>
-      <c r="J68" s="59" t="s">
+      <c r="J68" s="5" t="s">
         <v>994</v>
       </c>
-      <c r="K68" s="60">
+      <c r="K68" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>28.81095890410959</v>
       </c>
-      <c r="L68" s="47">
+      <c r="L68" s="46">
         <v>42862</v>
       </c>
-      <c r="M68" s="47">
+      <c r="M68" s="46">
         <v>29735613243</v>
       </c>
-      <c r="N68" s="47" t="s">
+      <c r="N68" s="46" t="s">
         <v>759</v>
       </c>
-      <c r="O68" s="51" t="s">
+      <c r="O68" s="50" t="s">
         <v>168</v>
       </c>
-      <c r="P68" s="47" t="s">
+      <c r="P68" s="46" t="s">
         <v>760</v>
       </c>
-      <c r="Q68" s="47" t="s">
+      <c r="Q68" s="46" t="s">
         <v>761</v>
       </c>
       <c r="R68" s="4" t="s">
@@ -8545,56 +8548,56 @@
       <c r="T68" s="19"/>
     </row>
     <row r="69" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="47">
+      <c r="A69" s="46">
         <v>93434</v>
       </c>
-      <c r="B69" s="47">
+      <c r="B69" s="46">
         <v>691</v>
       </c>
-      <c r="C69" s="48" t="s">
+      <c r="C69" s="47" t="s">
         <v>793</v>
       </c>
-      <c r="D69" s="47" t="s">
+      <c r="D69" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="E69" s="47" t="s">
+      <c r="E69" s="46" t="s">
         <v>794</v>
       </c>
-      <c r="F69" s="47" t="s">
+      <c r="F69" s="46" t="s">
         <v>794</v>
       </c>
-      <c r="G69" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H69" s="47" t="s">
+      <c r="G69" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" s="46" t="s">
         <v>23</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>1181</v>
       </c>
-      <c r="J69" s="59" t="s">
+      <c r="J69" s="5" t="s">
         <v>995</v>
       </c>
-      <c r="K69" s="60">
+      <c r="K69" s="58">
         <f t="shared" ca="1" si="0"/>
         <v>39.750684931506846</v>
       </c>
-      <c r="L69" s="47">
+      <c r="L69" s="46">
         <v>42000</v>
       </c>
-      <c r="M69" s="47">
+      <c r="M69" s="46">
         <v>28652447506</v>
       </c>
-      <c r="N69" s="47" t="s">
+      <c r="N69" s="46" t="s">
         <v>795</v>
       </c>
-      <c r="O69" s="51" t="s">
+      <c r="O69" s="50" t="s">
         <v>927</v>
       </c>
-      <c r="P69" s="47" t="s">
+      <c r="P69" s="46" t="s">
         <v>796</v>
       </c>
-      <c r="Q69" s="47" t="s">
+      <c r="Q69" s="46" t="s">
         <v>797</v>
       </c>
       <c r="R69" s="4" t="s">
@@ -8632,10 +8635,10 @@
       <c r="I70" s="8" t="s">
         <v>1182</v>
       </c>
-      <c r="J70" s="59" t="s">
+      <c r="J70" s="5" t="s">
         <v>996</v>
       </c>
-      <c r="K70" s="60">
+      <c r="K70" s="58">
         <f t="shared" ref="K70:K133" ca="1" si="1">(TODAY()-(DATEVALUE(SUBSTITUTE(J70,".","/"))))/(365)</f>
         <v>32.526027397260272</v>
       </c>
@@ -8693,10 +8696,10 @@
       <c r="I71" s="8" t="s">
         <v>1183</v>
       </c>
-      <c r="J71" s="59" t="s">
+      <c r="J71" s="5" t="s">
         <v>997</v>
       </c>
-      <c r="K71" s="60">
+      <c r="K71" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>49.2</v>
       </c>
@@ -8736,7 +8739,7 @@
       <c r="C72" s="6" t="s">
         <v>829</v>
       </c>
-      <c r="D72" s="47" t="s">
+      <c r="D72" s="46" t="s">
         <v>605</v>
       </c>
       <c r="E72" s="11" t="s">
@@ -8754,10 +8757,10 @@
       <c r="I72" s="8" t="s">
         <v>1184</v>
       </c>
-      <c r="J72" s="59" t="s">
+      <c r="J72" s="5" t="s">
         <v>998</v>
       </c>
-      <c r="K72" s="60">
+      <c r="K72" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>41.273972602739725</v>
       </c>
@@ -8814,10 +8817,10 @@
       <c r="I73" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="J73" s="59" t="s">
+      <c r="J73" s="5" t="s">
         <v>999</v>
       </c>
-      <c r="K73" s="60">
+      <c r="K73" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>47.07123287671233</v>
       </c>
@@ -8875,10 +8878,10 @@
       <c r="I74" s="8" t="s">
         <v>1186</v>
       </c>
-      <c r="J74" s="59" t="s">
+      <c r="J74" s="5" t="s">
         <v>1000</v>
       </c>
-      <c r="K74" s="60">
+      <c r="K74" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>56.906849315068492</v>
       </c>
@@ -8935,10 +8938,10 @@
       <c r="I75" s="8" t="s">
         <v>1187</v>
       </c>
-      <c r="J75" s="59" t="s">
+      <c r="J75" s="5" t="s">
         <v>1001</v>
       </c>
-      <c r="K75" s="60">
+      <c r="K75" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>35.520547945205479</v>
       </c>
@@ -8995,10 +8998,10 @@
       <c r="I76" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J76" s="59" t="s">
+      <c r="J76" s="5" t="s">
         <v>1002</v>
       </c>
-      <c r="K76" s="60">
+      <c r="K76" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>35.731506849315068</v>
       </c>
@@ -9055,10 +9058,10 @@
       <c r="I77" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J77" s="59" t="s">
+      <c r="J77" s="5" t="s">
         <v>1003</v>
       </c>
-      <c r="K77" s="60">
+      <c r="K77" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>52.739726027397261</v>
       </c>
@@ -9115,10 +9118,10 @@
       <c r="I78" s="8" t="s">
         <v>1188</v>
       </c>
-      <c r="J78" s="59" t="s">
+      <c r="J78" s="5" t="s">
         <v>1004</v>
       </c>
-      <c r="K78" s="60">
+      <c r="K78" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>59.358904109589041</v>
       </c>
@@ -9175,10 +9178,10 @@
       <c r="I79" s="8" t="s">
         <v>1189</v>
       </c>
-      <c r="J79" s="59" t="s">
+      <c r="J79" s="5" t="s">
         <v>1005</v>
       </c>
-      <c r="K79" s="60">
+      <c r="K79" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>40.364383561643834</v>
       </c>
@@ -9235,10 +9238,10 @@
       <c r="I80" s="8" t="s">
         <v>1190</v>
       </c>
-      <c r="J80" s="59" t="s">
+      <c r="J80" s="5" t="s">
         <v>1006</v>
       </c>
-      <c r="K80" s="60">
+      <c r="K80" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>48.964383561643835</v>
       </c>
@@ -9295,10 +9298,10 @@
       <c r="I81" s="8" t="s">
         <v>1191</v>
       </c>
-      <c r="J81" s="59" t="s">
+      <c r="J81" s="5" t="s">
         <v>1007</v>
       </c>
-      <c r="K81" s="60">
+      <c r="K81" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>55.627397260273973</v>
       </c>
@@ -9355,10 +9358,10 @@
       <c r="I82" s="8" t="s">
         <v>1192</v>
       </c>
-      <c r="J82" s="59" t="s">
+      <c r="J82" s="5" t="s">
         <v>1008</v>
       </c>
-      <c r="K82" s="60">
+      <c r="K82" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>29.013698630136986</v>
       </c>
@@ -9415,10 +9418,10 @@
       <c r="I83" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J83" s="59" t="s">
+      <c r="J83" s="5" t="s">
         <v>1009</v>
       </c>
-      <c r="K83" s="60">
+      <c r="K83" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>52.81095890410959</v>
       </c>
@@ -9475,10 +9478,10 @@
       <c r="I84" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J84" s="59" t="s">
+      <c r="J84" s="5" t="s">
         <v>1010</v>
       </c>
-      <c r="K84" s="60">
+      <c r="K84" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>45.767123287671232</v>
       </c>
@@ -9535,10 +9538,10 @@
       <c r="I85" s="8" t="s">
         <v>1193</v>
       </c>
-      <c r="J85" s="59" t="s">
+      <c r="J85" s="5" t="s">
         <v>1011</v>
       </c>
-      <c r="K85" s="60">
+      <c r="K85" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>60.145205479452052</v>
       </c>
@@ -9595,10 +9598,10 @@
       <c r="I86" s="8" t="s">
         <v>1194</v>
       </c>
-      <c r="J86" s="59" t="s">
+      <c r="J86" s="5" t="s">
         <v>1012</v>
       </c>
-      <c r="K86" s="60">
+      <c r="K86" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>54.197260273972603</v>
       </c>
@@ -9655,10 +9658,10 @@
       <c r="I87" s="8" t="s">
         <v>1195</v>
       </c>
-      <c r="J87" s="59" t="s">
+      <c r="J87" s="5" t="s">
         <v>1013</v>
       </c>
-      <c r="K87" s="60">
+      <c r="K87" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>40.953424657534249</v>
       </c>
@@ -9715,10 +9718,10 @@
       <c r="I88" s="8" t="s">
         <v>1196</v>
       </c>
-      <c r="J88" s="59" t="s">
+      <c r="J88" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="K88" s="60">
+      <c r="K88" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>58.060273972602737</v>
       </c>
@@ -9775,10 +9778,10 @@
       <c r="I89" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="J89" s="59" t="s">
+      <c r="J89" s="5" t="s">
         <v>1015</v>
       </c>
-      <c r="K89" s="60">
+      <c r="K89" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>44.895890410958906</v>
       </c>
@@ -9835,10 +9838,10 @@
       <c r="I90" s="8" t="s">
         <v>1198</v>
       </c>
-      <c r="J90" s="59" t="s">
+      <c r="J90" s="5" t="s">
         <v>1016</v>
       </c>
-      <c r="K90" s="60">
+      <c r="K90" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>55.821917808219176</v>
       </c>
@@ -9895,10 +9898,10 @@
       <c r="I91" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J91" s="59" t="s">
+      <c r="J91" s="5" t="s">
         <v>1017</v>
       </c>
-      <c r="K91" s="60">
+      <c r="K91" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>33.545205479452058</v>
       </c>
@@ -9955,10 +9958,10 @@
       <c r="I92" s="8" t="s">
         <v>1199</v>
       </c>
-      <c r="J92" s="59" t="s">
+      <c r="J92" s="5" t="s">
         <v>1018</v>
       </c>
-      <c r="K92" s="60">
+      <c r="K92" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>47.780821917808218</v>
       </c>
@@ -10015,10 +10018,10 @@
       <c r="I93" s="8" t="s">
         <v>1200</v>
       </c>
-      <c r="J93" s="59" t="s">
+      <c r="J93" s="5" t="s">
         <v>1019</v>
       </c>
-      <c r="K93" s="60">
+      <c r="K93" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>43.219178082191782</v>
       </c>
@@ -10076,10 +10079,10 @@
       <c r="I94" s="8" t="s">
         <v>1192</v>
       </c>
-      <c r="J94" s="59" t="s">
+      <c r="J94" s="5" t="s">
         <v>1020</v>
       </c>
-      <c r="K94" s="60">
+      <c r="K94" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>35.230136986301368</v>
       </c>
@@ -10136,10 +10139,10 @@
       <c r="I95" s="8" t="s">
         <v>1201</v>
       </c>
-      <c r="J95" s="59" t="s">
+      <c r="J95" s="5" t="s">
         <v>1021</v>
       </c>
-      <c r="K95" s="60">
+      <c r="K95" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>42.794520547945204</v>
       </c>
@@ -10196,10 +10199,10 @@
       <c r="I96" s="8" t="s">
         <v>1202</v>
       </c>
-      <c r="J96" s="59" t="s">
+      <c r="J96" s="5" t="s">
         <v>1022</v>
       </c>
-      <c r="K96" s="60">
+      <c r="K96" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>50.115068493150687</v>
       </c>
@@ -10256,10 +10259,10 @@
       <c r="I97" s="8" t="s">
         <v>1203</v>
       </c>
-      <c r="J97" s="59" t="s">
+      <c r="J97" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="K97" s="60">
+      <c r="K97" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>43.657534246575345</v>
       </c>
@@ -10316,10 +10319,10 @@
       <c r="I98" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="J98" s="59" t="s">
+      <c r="J98" s="5" t="s">
         <v>1024</v>
       </c>
-      <c r="K98" s="60">
+      <c r="K98" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>41.265753424657532</v>
       </c>
@@ -10376,10 +10379,10 @@
       <c r="I99" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J99" s="59" t="s">
+      <c r="J99" s="5" t="s">
         <v>1025</v>
       </c>
-      <c r="K99" s="60">
+      <c r="K99" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>39.983561643835614</v>
       </c>
@@ -10436,10 +10439,10 @@
       <c r="I100" s="8" t="s">
         <v>1174</v>
       </c>
-      <c r="J100" s="59" t="s">
+      <c r="J100" s="5" t="s">
         <v>1026</v>
       </c>
-      <c r="K100" s="60">
+      <c r="K100" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>37.084931506849315</v>
       </c>
@@ -10496,10 +10499,10 @@
       <c r="I101" s="8" t="s">
         <v>1205</v>
       </c>
-      <c r="J101" s="59" t="s">
+      <c r="J101" s="5" t="s">
         <v>1027</v>
       </c>
-      <c r="K101" s="60">
+      <c r="K101" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>58.419178082191777</v>
       </c>
@@ -10556,10 +10559,10 @@
       <c r="I102" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J102" s="59" t="s">
+      <c r="J102" s="5" t="s">
         <v>1028</v>
       </c>
-      <c r="K102" s="60">
+      <c r="K102" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>57.364383561643834</v>
       </c>
@@ -10616,10 +10619,10 @@
       <c r="I103" s="8" t="s">
         <v>1206</v>
       </c>
-      <c r="J103" s="59" t="s">
+      <c r="J103" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="K103" s="60">
+      <c r="K103" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>37.802739726027397</v>
       </c>
@@ -10676,10 +10679,10 @@
       <c r="I104" s="8" t="s">
         <v>1207</v>
       </c>
-      <c r="J104" s="59" t="s">
+      <c r="J104" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="K104" s="60">
+      <c r="K104" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>30.301369863013697</v>
       </c>
@@ -10736,10 +10739,10 @@
       <c r="I105" s="8" t="s">
         <v>1208</v>
       </c>
-      <c r="J105" s="59" t="s">
+      <c r="J105" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="K105" s="60">
+      <c r="K105" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>50.660273972602738</v>
       </c>
@@ -10796,10 +10799,10 @@
       <c r="I106" s="8" t="s">
         <v>1209</v>
       </c>
-      <c r="J106" s="59" t="s">
+      <c r="J106" s="5" t="s">
         <v>1032</v>
       </c>
-      <c r="K106" s="60">
+      <c r="K106" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>26.419178082191781</v>
       </c>
@@ -10856,10 +10859,10 @@
       <c r="I107" s="8" t="s">
         <v>1210</v>
       </c>
-      <c r="J107" s="59" t="s">
+      <c r="J107" s="5" t="s">
         <v>1033</v>
       </c>
-      <c r="K107" s="60">
+      <c r="K107" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>43.128767123287673</v>
       </c>
@@ -10916,10 +10919,10 @@
       <c r="I108" s="8" t="s">
         <v>1211</v>
       </c>
-      <c r="J108" s="59" t="s">
+      <c r="J108" s="5" t="s">
         <v>1034</v>
       </c>
-      <c r="K108" s="60">
+      <c r="K108" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>37.775342465753425</v>
       </c>
@@ -10976,10 +10979,10 @@
       <c r="I109" s="8" t="s">
         <v>1212</v>
       </c>
-      <c r="J109" s="59" t="s">
+      <c r="J109" s="5" t="s">
         <v>1035</v>
       </c>
-      <c r="K109" s="60">
+      <c r="K109" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>38.739726027397261</v>
       </c>
@@ -11036,10 +11039,10 @@
       <c r="I110" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="J110" s="59" t="s">
+      <c r="J110" s="5" t="s">
         <v>1036</v>
       </c>
-      <c r="K110" s="60">
+      <c r="K110" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>39.021917808219179</v>
       </c>
@@ -11096,10 +11099,10 @@
       <c r="I111" s="8" t="s">
         <v>1213</v>
       </c>
-      <c r="J111" s="59" t="s">
+      <c r="J111" s="5" t="s">
         <v>1037</v>
       </c>
-      <c r="K111" s="60">
+      <c r="K111" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>46.531506849315072</v>
       </c>
@@ -11156,10 +11159,10 @@
       <c r="I112" s="8" t="s">
         <v>1214</v>
       </c>
-      <c r="J112" s="59" t="s">
+      <c r="J112" s="5" t="s">
         <v>1038</v>
       </c>
-      <c r="K112" s="60">
+      <c r="K112" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>38.561643835616437</v>
       </c>
@@ -11216,10 +11219,10 @@
       <c r="I113" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="J113" s="59" t="s">
+      <c r="J113" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="K113" s="60">
+      <c r="K113" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>46.016438356164386</v>
       </c>
@@ -11276,10 +11279,10 @@
       <c r="I114" s="8" t="s">
         <v>1128</v>
       </c>
-      <c r="J114" s="59" t="s">
+      <c r="J114" s="5" t="s">
         <v>1040</v>
       </c>
-      <c r="K114" s="60">
+      <c r="K114" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>51.934246575342463</v>
       </c>
@@ -11336,10 +11339,10 @@
       <c r="I115" s="8" t="s">
         <v>1192</v>
       </c>
-      <c r="J115" s="59" t="s">
+      <c r="J115" s="5" t="s">
         <v>1041</v>
       </c>
-      <c r="K115" s="60">
+      <c r="K115" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>36.668493150684931</v>
       </c>
@@ -11396,10 +11399,10 @@
       <c r="I116" s="8" t="s">
         <v>1192</v>
       </c>
-      <c r="J116" s="59" t="s">
+      <c r="J116" s="5" t="s">
         <v>1042</v>
       </c>
-      <c r="K116" s="60">
+      <c r="K116" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>36.893150684931506</v>
       </c>
@@ -11456,10 +11459,10 @@
       <c r="I117" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="J117" s="59" t="s">
+      <c r="J117" s="5" t="s">
         <v>1043</v>
       </c>
-      <c r="K117" s="60">
+      <c r="K117" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>27.473972602739725</v>
       </c>
@@ -11516,10 +11519,10 @@
       <c r="I118" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J118" s="59" t="s">
+      <c r="J118" s="5" t="s">
         <v>1044</v>
       </c>
-      <c r="K118" s="60">
+      <c r="K118" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>40.495890410958907</v>
       </c>
@@ -11576,10 +11579,10 @@
       <c r="I119" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="J119" s="59" t="s">
+      <c r="J119" s="5" t="s">
         <v>1045</v>
       </c>
-      <c r="K119" s="60">
+      <c r="K119" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>41.169863013698631</v>
       </c>
@@ -11636,10 +11639,10 @@
       <c r="I120" s="8" t="s">
         <v>1217</v>
       </c>
-      <c r="J120" s="59" t="s">
+      <c r="J120" s="5" t="s">
         <v>1046</v>
       </c>
-      <c r="K120" s="60">
+      <c r="K120" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>45.969863013698628</v>
       </c>
@@ -11696,10 +11699,10 @@
       <c r="I121" s="8" t="s">
         <v>1218</v>
       </c>
-      <c r="J121" s="59" t="s">
+      <c r="J121" s="5" t="s">
         <v>1047</v>
       </c>
-      <c r="K121" s="60">
+      <c r="K121" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>38.290410958904111</v>
       </c>
@@ -11756,10 +11759,10 @@
       <c r="I122" s="8" t="s">
         <v>1219</v>
       </c>
-      <c r="J122" s="59" t="s">
+      <c r="J122" s="5" t="s">
         <v>1048</v>
       </c>
-      <c r="K122" s="60">
+      <c r="K122" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>60.435616438356163</v>
       </c>
@@ -11816,10 +11819,10 @@
       <c r="I123" s="8" t="s">
         <v>1220</v>
       </c>
-      <c r="J123" s="59" t="s">
+      <c r="J123" s="5" t="s">
         <v>1049</v>
       </c>
-      <c r="K123" s="60">
+      <c r="K123" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>38.016438356164386</v>
       </c>
@@ -11876,10 +11879,10 @@
       <c r="I124" s="8" t="s">
         <v>1221</v>
       </c>
-      <c r="J124" s="59" t="s">
+      <c r="J124" s="5" t="s">
         <v>1050</v>
       </c>
-      <c r="K124" s="60">
+      <c r="K124" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>45.134246575342466</v>
       </c>
@@ -11909,56 +11912,56 @@
       </c>
     </row>
     <row r="125" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="47">
+      <c r="A125" s="46">
         <v>93427</v>
       </c>
-      <c r="B125" s="47">
+      <c r="B125" s="46">
         <v>685</v>
       </c>
-      <c r="C125" s="48" t="s">
+      <c r="C125" s="47" t="s">
         <v>762</v>
       </c>
-      <c r="D125" s="47" t="s">
+      <c r="D125" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E125" s="47" t="s">
+      <c r="E125" s="46" t="s">
         <v>763</v>
       </c>
-      <c r="F125" s="47" t="s">
+      <c r="F125" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="G125" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H125" s="47" t="s">
+      <c r="G125" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H125" s="46" t="s">
         <v>23</v>
       </c>
       <c r="I125" s="8" t="s">
         <v>1222</v>
       </c>
-      <c r="J125" s="59" t="s">
+      <c r="J125" s="5" t="s">
         <v>1051</v>
       </c>
-      <c r="K125" s="60">
+      <c r="K125" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>40.764383561643832</v>
       </c>
-      <c r="L125" s="47">
+      <c r="L125" s="46">
         <v>42863</v>
       </c>
-      <c r="M125" s="47">
+      <c r="M125" s="46">
         <v>28535685852</v>
       </c>
-      <c r="N125" s="47" t="s">
+      <c r="N125" s="46" t="s">
         <v>764</v>
       </c>
-      <c r="O125" s="51" t="s">
+      <c r="O125" s="50" t="s">
         <v>927</v>
       </c>
-      <c r="P125" s="47" t="s">
+      <c r="P125" s="46" t="s">
         <v>765</v>
       </c>
-      <c r="Q125" s="47" t="s">
+      <c r="Q125" s="46" t="s">
         <v>766</v>
       </c>
       <c r="R125" s="4" t="s">
@@ -11996,10 +11999,10 @@
       <c r="I126" s="8" t="s">
         <v>1223</v>
       </c>
-      <c r="J126" s="59" t="s">
+      <c r="J126" s="5" t="s">
         <v>1052</v>
       </c>
-      <c r="K126" s="60">
+      <c r="K126" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>42.049315068493151</v>
       </c>
@@ -12056,10 +12059,10 @@
       <c r="I127" s="8" t="s">
         <v>1224</v>
       </c>
-      <c r="J127" s="59" t="s">
+      <c r="J127" s="5" t="s">
         <v>1053</v>
       </c>
-      <c r="K127" s="60">
+      <c r="K127" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>31.295890410958904</v>
       </c>
@@ -12116,10 +12119,10 @@
       <c r="I128" s="8" t="s">
         <v>1225</v>
       </c>
-      <c r="J128" s="59" t="s">
+      <c r="J128" s="5" t="s">
         <v>1054</v>
       </c>
-      <c r="K128" s="60">
+      <c r="K128" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>45.301369863013697</v>
       </c>
@@ -12176,10 +12179,10 @@
       <c r="I129" s="8" t="s">
         <v>1169</v>
       </c>
-      <c r="J129" s="59" t="s">
+      <c r="J129" s="5" t="s">
         <v>1055</v>
       </c>
-      <c r="K129" s="60">
+      <c r="K129" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>42.838356164383562</v>
       </c>
@@ -12236,10 +12239,10 @@
       <c r="I130" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J130" s="59" t="s">
+      <c r="J130" s="5" t="s">
         <v>1056</v>
       </c>
-      <c r="K130" s="60">
+      <c r="K130" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>36</v>
       </c>
@@ -12296,10 +12299,10 @@
       <c r="I131" s="8" t="s">
         <v>1226</v>
       </c>
-      <c r="J131" s="59" t="s">
+      <c r="J131" s="5" t="s">
         <v>1057</v>
       </c>
-      <c r="K131" s="60">
+      <c r="K131" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>42.56986301369863</v>
       </c>
@@ -12356,10 +12359,10 @@
       <c r="I132" s="8" t="s">
         <v>1227</v>
       </c>
-      <c r="J132" s="59" t="s">
+      <c r="J132" s="5" t="s">
         <v>1058</v>
       </c>
-      <c r="K132" s="60">
+      <c r="K132" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>39.890410958904113</v>
       </c>
@@ -12416,10 +12419,10 @@
       <c r="I133" s="8" t="s">
         <v>1228</v>
       </c>
-      <c r="J133" s="59" t="s">
+      <c r="J133" s="5" t="s">
         <v>1059</v>
       </c>
-      <c r="K133" s="60">
+      <c r="K133" s="58">
         <f t="shared" ca="1" si="1"/>
         <v>39.413698630136984</v>
       </c>
@@ -12476,10 +12479,10 @@
       <c r="I134" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J134" s="59" t="s">
+      <c r="J134" s="5" t="s">
         <v>1060</v>
       </c>
-      <c r="K134" s="60">
+      <c r="K134" s="58">
         <f t="shared" ref="K134:K197" ca="1" si="2">(TODAY()-(DATEVALUE(SUBSTITUTE(J134,".","/"))))/(365)</f>
         <v>41.81095890410959</v>
       </c>
@@ -12536,10 +12539,10 @@
       <c r="I135" s="8" t="s">
         <v>1229</v>
       </c>
-      <c r="J135" s="59" t="s">
+      <c r="J135" s="5" t="s">
         <v>1061</v>
       </c>
-      <c r="K135" s="60">
+      <c r="K135" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>32.942465753424656</v>
       </c>
@@ -12596,10 +12599,10 @@
       <c r="I136" s="8" t="s">
         <v>1230</v>
       </c>
-      <c r="J136" s="59" t="s">
+      <c r="J136" s="5" t="s">
         <v>1062</v>
       </c>
-      <c r="K136" s="60">
+      <c r="K136" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>41.364383561643834</v>
       </c>
@@ -12618,7 +12621,7 @@
       <c r="P136" s="14" t="s">
         <v>743</v>
       </c>
-      <c r="Q136" s="57" t="s">
+      <c r="Q136" s="56" t="s">
         <v>744</v>
       </c>
       <c r="R136" s="18" t="s">
@@ -12656,10 +12659,10 @@
       <c r="I137" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J137" s="59" t="s">
+      <c r="J137" s="5" t="s">
         <v>1063</v>
       </c>
-      <c r="K137" s="60">
+      <c r="K137" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>49.6</v>
       </c>
@@ -12716,10 +12719,10 @@
       <c r="I138" s="8" t="s">
         <v>1231</v>
       </c>
-      <c r="J138" s="59" t="s">
+      <c r="J138" s="5" t="s">
         <v>1064</v>
       </c>
-      <c r="K138" s="60">
+      <c r="K138" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>41.38356164383562</v>
       </c>
@@ -12776,10 +12779,10 @@
       <c r="I139" s="8" t="s">
         <v>1232</v>
       </c>
-      <c r="J139" s="59" t="s">
+      <c r="J139" s="5" t="s">
         <v>1065</v>
       </c>
-      <c r="K139" s="60">
+      <c r="K139" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>40.641095890410959</v>
       </c>
@@ -12836,10 +12839,10 @@
       <c r="I140" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J140" s="59" t="s">
+      <c r="J140" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="K140" s="60">
+      <c r="K140" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>46.016438356164386</v>
       </c>
@@ -12896,10 +12899,10 @@
       <c r="I141" s="8" t="s">
         <v>1161</v>
       </c>
-      <c r="J141" s="59" t="s">
+      <c r="J141" s="5" t="s">
         <v>1066</v>
       </c>
-      <c r="K141" s="60">
+      <c r="K141" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>40.958904109589042</v>
       </c>
@@ -12956,10 +12959,10 @@
       <c r="I142" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J142" s="59" t="s">
+      <c r="J142" s="5" t="s">
         <v>1067</v>
       </c>
-      <c r="K142" s="60">
+      <c r="K142" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>40.775342465753425</v>
       </c>
@@ -13016,10 +13019,10 @@
       <c r="I143" s="8" t="s">
         <v>1233</v>
       </c>
-      <c r="J143" s="59" t="s">
+      <c r="J143" s="5" t="s">
         <v>1068</v>
       </c>
-      <c r="K143" s="60">
+      <c r="K143" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>40.698630136986303</v>
       </c>
@@ -13076,10 +13079,10 @@
       <c r="I144" s="8" t="s">
         <v>1234</v>
       </c>
-      <c r="J144" s="59" t="s">
+      <c r="J144" s="5" t="s">
         <v>1069</v>
       </c>
-      <c r="K144" s="60">
+      <c r="K144" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>43.591780821917808</v>
       </c>
@@ -13136,10 +13139,10 @@
       <c r="I145" s="8" t="s">
         <v>1235</v>
       </c>
-      <c r="J145" s="59" t="s">
+      <c r="J145" s="5" t="s">
         <v>1070</v>
       </c>
-      <c r="K145" s="60">
+      <c r="K145" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>48.101369863013701</v>
       </c>
@@ -13197,10 +13200,10 @@
       <c r="I146" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="J146" s="59" t="s">
+      <c r="J146" s="5" t="s">
         <v>1071</v>
       </c>
-      <c r="K146" s="60">
+      <c r="K146" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>40.545205479452058</v>
       </c>
@@ -13257,10 +13260,10 @@
       <c r="I147" s="8" t="s">
         <v>1237</v>
       </c>
-      <c r="J147" s="59" t="s">
+      <c r="J147" s="5" t="s">
         <v>1072</v>
       </c>
-      <c r="K147" s="60">
+      <c r="K147" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>41.446575342465756</v>
       </c>
@@ -13317,10 +13320,10 @@
       <c r="I148" s="8" t="s">
         <v>1238</v>
       </c>
-      <c r="J148" s="59" t="s">
+      <c r="J148" s="5" t="s">
         <v>1073</v>
       </c>
-      <c r="K148" s="60">
+      <c r="K148" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>48.92876712328767</v>
       </c>
@@ -13377,10 +13380,10 @@
       <c r="I149" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="J149" s="59" t="s">
+      <c r="J149" s="5" t="s">
         <v>1074</v>
       </c>
-      <c r="K149" s="60">
+      <c r="K149" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>54.780821917808218</v>
       </c>
@@ -13437,10 +13440,10 @@
       <c r="I150" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="J150" s="59" t="s">
+      <c r="J150" s="5" t="s">
         <v>1075</v>
       </c>
-      <c r="K150" s="60">
+      <c r="K150" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>39.753424657534246</v>
       </c>
@@ -13497,10 +13500,10 @@
       <c r="I151" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="J151" s="59" t="s">
+      <c r="J151" s="5" t="s">
         <v>1076</v>
       </c>
-      <c r="K151" s="60">
+      <c r="K151" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>39.243835616438353</v>
       </c>
@@ -13557,10 +13560,10 @@
       <c r="I152" s="8" t="s">
         <v>1192</v>
       </c>
-      <c r="J152" s="59" t="s">
+      <c r="J152" s="5" t="s">
         <v>1077</v>
       </c>
-      <c r="K152" s="60">
+      <c r="K152" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>33.493150684931507</v>
       </c>
@@ -13617,10 +13620,10 @@
       <c r="I153" s="8" t="s">
         <v>1241</v>
       </c>
-      <c r="J153" s="59" t="s">
+      <c r="J153" s="5" t="s">
         <v>1078</v>
       </c>
-      <c r="K153" s="60">
+      <c r="K153" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>47.991780821917807</v>
       </c>
@@ -13677,10 +13680,10 @@
       <c r="I154" s="8" t="s">
         <v>1242</v>
       </c>
-      <c r="J154" s="59" t="s">
+      <c r="J154" s="5" t="s">
         <v>1079</v>
       </c>
-      <c r="K154" s="60">
+      <c r="K154" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>45.07123287671233</v>
       </c>
@@ -13737,10 +13740,10 @@
       <c r="I155" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J155" s="59" t="s">
+      <c r="J155" s="5" t="s">
         <v>1080</v>
       </c>
-      <c r="K155" s="60">
+      <c r="K155" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>36.12054794520548</v>
       </c>
@@ -13797,10 +13800,10 @@
       <c r="I156" s="8" t="s">
         <v>1243</v>
       </c>
-      <c r="J156" s="59" t="s">
+      <c r="J156" s="5" t="s">
         <v>1081</v>
       </c>
-      <c r="K156" s="60">
+      <c r="K156" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>44.328767123287669</v>
       </c>
@@ -13857,10 +13860,10 @@
       <c r="I157" s="8" t="s">
         <v>1244</v>
       </c>
-      <c r="J157" s="59" t="s">
+      <c r="J157" s="5" t="s">
         <v>1082</v>
       </c>
-      <c r="K157" s="60">
+      <c r="K157" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>45.906849315068492</v>
       </c>
@@ -13917,10 +13920,10 @@
       <c r="I158" s="8" t="s">
         <v>1245</v>
       </c>
-      <c r="J158" s="59" t="s">
+      <c r="J158" s="5" t="s">
         <v>1083</v>
       </c>
-      <c r="K158" s="60">
+      <c r="K158" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>36.526027397260272</v>
       </c>
@@ -13978,10 +13981,10 @@
       <c r="I159" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="J159" s="59" t="s">
+      <c r="J159" s="5" t="s">
         <v>1084</v>
       </c>
-      <c r="K159" s="60">
+      <c r="K159" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>42.276712328767125</v>
       </c>
@@ -14038,10 +14041,10 @@
       <c r="I160" s="8" t="s">
         <v>1246</v>
       </c>
-      <c r="J160" s="59" t="s">
+      <c r="J160" s="5" t="s">
         <v>1085</v>
       </c>
-      <c r="K160" s="60">
+      <c r="K160" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>53.753424657534246</v>
       </c>
@@ -14098,10 +14101,10 @@
       <c r="I161" s="8" t="s">
         <v>1247</v>
       </c>
-      <c r="J161" s="59" t="s">
+      <c r="J161" s="5" t="s">
         <v>1086</v>
       </c>
-      <c r="K161" s="60">
+      <c r="K161" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>38.446575342465756</v>
       </c>
@@ -14158,10 +14161,10 @@
       <c r="I162" s="8" t="s">
         <v>1220</v>
       </c>
-      <c r="J162" s="59" t="s">
+      <c r="J162" s="5" t="s">
         <v>1087</v>
       </c>
-      <c r="K162" s="60">
+      <c r="K162" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>53.939726027397263</v>
       </c>
@@ -14218,10 +14221,10 @@
       <c r="I163" s="8" t="s">
         <v>1248</v>
       </c>
-      <c r="J163" s="59" t="s">
+      <c r="J163" s="5" t="s">
         <v>1088</v>
       </c>
-      <c r="K163" s="60">
+      <c r="K163" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>60.452054794520549</v>
       </c>
@@ -14278,10 +14281,10 @@
       <c r="I164" s="8" t="s">
         <v>1215</v>
       </c>
-      <c r="J164" s="59" t="s">
+      <c r="J164" s="5" t="s">
         <v>1089</v>
       </c>
-      <c r="K164" s="60">
+      <c r="K164" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>45.194520547945203</v>
       </c>
@@ -14291,16 +14294,16 @@
       <c r="M164" s="18">
         <v>28052408693</v>
       </c>
-      <c r="N164" s="36" t="s">
+      <c r="N164" s="35" t="s">
         <v>882</v>
       </c>
-      <c r="O164" s="43" t="s">
+      <c r="O164" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P164" s="40" t="s">
+      <c r="P164" s="39" t="s">
         <v>883</v>
       </c>
-      <c r="Q164" s="53" t="s">
+      <c r="Q164" s="52" t="s">
         <v>884</v>
       </c>
       <c r="R164" s="18" t="s">
@@ -14339,10 +14342,10 @@
       <c r="I165" s="8" t="s">
         <v>1194</v>
       </c>
-      <c r="J165" s="59" t="s">
+      <c r="J165" s="5" t="s">
         <v>1090</v>
       </c>
-      <c r="K165" s="60">
+      <c r="K165" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>36.701369863013696</v>
       </c>
@@ -14352,16 +14355,16 @@
       <c r="M165" s="12">
         <v>28935612139</v>
       </c>
-      <c r="N165" s="36" t="s">
+      <c r="N165" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="O165" s="43" t="s">
+      <c r="O165" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P165" s="38" t="s">
+      <c r="P165" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="Q165" s="54" t="s">
+      <c r="Q165" s="53" t="s">
         <v>317</v>
       </c>
       <c r="R165" s="18" t="s">
@@ -14400,10 +14403,10 @@
       <c r="I166" s="8" t="s">
         <v>1249</v>
       </c>
-      <c r="J166" s="59" t="s">
+      <c r="J166" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="K166" s="60">
+      <c r="K166" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>45.780821917808218</v>
       </c>
@@ -14413,16 +14416,16 @@
       <c r="M166" s="12">
         <v>28060807651</v>
       </c>
-      <c r="N166" s="36" t="s">
+      <c r="N166" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="O166" s="43" t="s">
+      <c r="O166" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P166" s="38" t="s">
+      <c r="P166" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="Q166" s="54" t="s">
+      <c r="Q166" s="53" t="s">
         <v>112</v>
       </c>
       <c r="R166" s="18" t="s">
@@ -14461,10 +14464,10 @@
       <c r="I167" s="8" t="s">
         <v>1250</v>
       </c>
-      <c r="J167" s="59" t="s">
+      <c r="J167" s="5" t="s">
         <v>931</v>
       </c>
-      <c r="K167" s="60">
+      <c r="K167" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>54.142465753424659</v>
       </c>
@@ -14474,16 +14477,16 @@
       <c r="M167" s="12">
         <v>27276400357</v>
       </c>
-      <c r="N167" s="36" t="s">
+      <c r="N167" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="O167" s="43" t="s">
+      <c r="O167" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P167" s="38" t="s">
+      <c r="P167" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="Q167" s="54" t="s">
+      <c r="Q167" s="53" t="s">
         <v>55</v>
       </c>
       <c r="R167" s="18" t="s">
@@ -14522,10 +14525,10 @@
       <c r="I168" s="8" t="s">
         <v>1251</v>
       </c>
-      <c r="J168" s="59" t="s">
+      <c r="J168" s="5" t="s">
         <v>1092</v>
       </c>
-      <c r="K168" s="60">
+      <c r="K168" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>41.679452054794524</v>
       </c>
@@ -14535,16 +14538,16 @@
       <c r="M168" s="12">
         <v>28435612607</v>
       </c>
-      <c r="N168" s="36" t="s">
+      <c r="N168" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="O168" s="43" t="s">
+      <c r="O168" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P168" s="38" t="s">
+      <c r="P168" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="Q168" s="53" t="s">
+      <c r="Q168" s="52" t="s">
         <v>277</v>
       </c>
       <c r="R168" s="18" t="s">
@@ -14583,10 +14586,10 @@
       <c r="I169" s="8" t="s">
         <v>1252</v>
       </c>
-      <c r="J169" s="59" t="s">
+      <c r="J169" s="5" t="s">
         <v>1093</v>
       </c>
-      <c r="K169" s="60">
+      <c r="K169" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>34.084931506849315</v>
       </c>
@@ -14596,16 +14599,16 @@
       <c r="M169" s="12">
         <v>29235652642</v>
       </c>
-      <c r="N169" s="36" t="s">
+      <c r="N169" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="O169" s="43" t="s">
+      <c r="O169" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="P169" s="38" t="s">
+      <c r="P169" s="37" t="s">
         <v>372</v>
       </c>
-      <c r="Q169" s="54" t="s">
+      <c r="Q169" s="53" t="s">
         <v>373</v>
       </c>
       <c r="R169" s="18" t="s">
@@ -14644,10 +14647,10 @@
       <c r="I170" s="8" t="s">
         <v>1253</v>
       </c>
-      <c r="J170" s="59" t="s">
+      <c r="J170" s="5" t="s">
         <v>1094</v>
       </c>
-      <c r="K170" s="60">
+      <c r="K170" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>27.742465753424657</v>
       </c>
@@ -14657,16 +14660,16 @@
       <c r="M170" s="12">
         <v>29835609599</v>
       </c>
-      <c r="N170" s="36" t="s">
+      <c r="N170" s="35" t="s">
         <v>717</v>
       </c>
-      <c r="O170" s="43" t="s">
+      <c r="O170" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P170" s="38" t="s">
+      <c r="P170" s="37" t="s">
         <v>718</v>
       </c>
-      <c r="Q170" s="54" t="s">
+      <c r="Q170" s="53" t="s">
         <v>719</v>
       </c>
       <c r="R170" s="18" t="s">
@@ -14705,10 +14708,10 @@
       <c r="I171" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J171" s="59" t="s">
+      <c r="J171" s="5" t="s">
         <v>1095</v>
       </c>
-      <c r="K171" s="60">
+      <c r="K171" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>36.643835616438359</v>
       </c>
@@ -14718,16 +14721,16 @@
       <c r="M171" s="12">
         <v>28935621683</v>
       </c>
-      <c r="N171" s="36" t="s">
+      <c r="N171" s="35" t="s">
         <v>431</v>
       </c>
-      <c r="O171" s="43" t="s">
+      <c r="O171" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P171" s="38" t="s">
+      <c r="P171" s="37" t="s">
         <v>432</v>
       </c>
-      <c r="Q171" s="54" t="s">
+      <c r="Q171" s="53" t="s">
         <v>433</v>
       </c>
       <c r="R171" s="18" t="s">
@@ -14766,10 +14769,10 @@
       <c r="I172" s="8" t="s">
         <v>1254</v>
       </c>
-      <c r="J172" s="59" t="s">
+      <c r="J172" s="5" t="s">
         <v>1096</v>
       </c>
-      <c r="K172" s="60">
+      <c r="K172" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>50.238356164383561</v>
       </c>
@@ -14779,16 +14782,16 @@
       <c r="M172" s="12">
         <v>27535620013</v>
       </c>
-      <c r="N172" s="36" t="s">
+      <c r="N172" s="35" t="s">
         <v>738</v>
       </c>
-      <c r="O172" s="43" t="s">
+      <c r="O172" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P172" s="38" t="s">
+      <c r="P172" s="37" t="s">
         <v>739</v>
       </c>
-      <c r="Q172" s="54" t="s">
+      <c r="Q172" s="53" t="s">
         <v>740</v>
       </c>
       <c r="R172" s="18" t="s">
@@ -14827,10 +14830,10 @@
       <c r="I173" s="8" t="s">
         <v>1255</v>
       </c>
-      <c r="J173" s="59" t="s">
+      <c r="J173" s="5" t="s">
         <v>1097</v>
       </c>
-      <c r="K173" s="60">
+      <c r="K173" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>51.701369863013696</v>
       </c>
@@ -14840,16 +14843,16 @@
       <c r="M173" s="12">
         <v>27414410278</v>
       </c>
-      <c r="N173" s="36" t="s">
+      <c r="N173" s="35" t="s">
         <v>532</v>
       </c>
-      <c r="O173" s="43" t="s">
+      <c r="O173" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="P173" s="38" t="s">
+      <c r="P173" s="37" t="s">
         <v>533</v>
       </c>
-      <c r="Q173" s="54" t="s">
+      <c r="Q173" s="53" t="s">
         <v>534</v>
       </c>
       <c r="R173" s="18" t="s">
@@ -14888,10 +14891,10 @@
       <c r="I174" s="8" t="s">
         <v>1256</v>
       </c>
-      <c r="J174" s="59" t="s">
+      <c r="J174" s="5" t="s">
         <v>1098</v>
       </c>
-      <c r="K174" s="60">
+      <c r="K174" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>30.756164383561643</v>
       </c>
@@ -14948,10 +14951,10 @@
       <c r="I175" s="8" t="s">
         <v>1192</v>
       </c>
-      <c r="J175" s="59" t="s">
+      <c r="J175" s="5" t="s">
         <v>1099</v>
       </c>
-      <c r="K175" s="60">
+      <c r="K175" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>41.397260273972606</v>
       </c>
@@ -15008,10 +15011,10 @@
       <c r="I176" s="8" t="s">
         <v>1257</v>
       </c>
-      <c r="J176" s="59" t="s">
+      <c r="J176" s="5" t="s">
         <v>1100</v>
       </c>
-      <c r="K176" s="60">
+      <c r="K176" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>33.457534246575342</v>
       </c>
@@ -15069,10 +15072,10 @@
       <c r="I177" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="J177" s="59" t="s">
+      <c r="J177" s="5" t="s">
         <v>1101</v>
       </c>
-      <c r="K177" s="60">
+      <c r="K177" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>43.720547945205482</v>
       </c>
@@ -15082,16 +15085,16 @@
       <c r="M177" s="12">
         <v>28235648331</v>
       </c>
-      <c r="N177" s="36" t="s">
+      <c r="N177" s="35" t="s">
         <v>599</v>
       </c>
       <c r="O177" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P177" s="38" t="s">
+      <c r="P177" s="37" t="s">
         <v>600</v>
       </c>
-      <c r="Q177" s="52" t="s">
+      <c r="Q177" s="51" t="s">
         <v>601</v>
       </c>
       <c r="R177" s="18" t="s">
@@ -15130,10 +15133,10 @@
       <c r="I178" s="8" t="s">
         <v>1258</v>
       </c>
-      <c r="J178" s="59" t="s">
+      <c r="J178" s="5" t="s">
         <v>1102</v>
       </c>
-      <c r="K178" s="60">
+      <c r="K178" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>45.630136986301373</v>
       </c>
@@ -15143,16 +15146,16 @@
       <c r="M178" s="12">
         <v>28052413008</v>
       </c>
-      <c r="N178" s="36" t="s">
+      <c r="N178" s="35" t="s">
         <v>154</v>
       </c>
       <c r="O178" s="16" t="s">
         <v>927</v>
       </c>
-      <c r="P178" s="38" t="s">
+      <c r="P178" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="Q178" s="52" t="s">
+      <c r="Q178" s="51" t="s">
         <v>156</v>
       </c>
       <c r="R178" s="18" t="s">
@@ -15161,7 +15164,7 @@
       <c r="S178" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="T178" s="41"/>
+      <c r="T178" s="40"/>
     </row>
     <row r="179" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="12">
@@ -15191,10 +15194,10 @@
       <c r="I179" s="8" t="s">
         <v>1259</v>
       </c>
-      <c r="J179" s="59" t="s">
+      <c r="J179" s="5" t="s">
         <v>1103</v>
       </c>
-      <c r="K179" s="60">
+      <c r="K179" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>34.69041095890411</v>
       </c>
@@ -15204,16 +15207,16 @@
       <c r="M179" s="12">
         <v>29105010001</v>
       </c>
-      <c r="N179" s="50" t="s">
+      <c r="N179" s="49" t="s">
         <v>591</v>
       </c>
       <c r="O179" s="16" t="s">
         <v>927</v>
       </c>
-      <c r="P179" s="38" t="s">
+      <c r="P179" s="37" t="s">
         <v>592</v>
       </c>
-      <c r="Q179" s="52" t="s">
+      <c r="Q179" s="51" t="s">
         <v>593</v>
       </c>
       <c r="R179" s="18" t="s">
@@ -15222,7 +15225,7 @@
       <c r="S179" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="T179" s="41"/>
+      <c r="T179" s="40"/>
     </row>
     <row r="180" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12">
@@ -15252,10 +15255,10 @@
       <c r="I180" s="8" t="s">
         <v>1260</v>
       </c>
-      <c r="J180" s="59" t="s">
+      <c r="J180" s="5" t="s">
         <v>930</v>
       </c>
-      <c r="K180" s="60">
+      <c r="K180" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>39.860273972602741</v>
       </c>
@@ -15265,16 +15268,16 @@
       <c r="M180" s="12">
         <v>28652414311</v>
       </c>
-      <c r="N180" s="36" t="s">
+      <c r="N180" s="35" t="s">
         <v>851</v>
       </c>
       <c r="O180" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P180" s="40" t="s">
+      <c r="P180" s="39" t="s">
         <v>852</v>
       </c>
-      <c r="Q180" s="39" t="s">
+      <c r="Q180" s="38" t="s">
         <v>853</v>
       </c>
       <c r="R180" s="18" t="s">
@@ -15313,10 +15316,10 @@
       <c r="I181" s="8" t="s">
         <v>1261</v>
       </c>
-      <c r="J181" s="59" t="s">
+      <c r="J181" s="5" t="s">
         <v>1104</v>
       </c>
-      <c r="K181" s="60">
+      <c r="K181" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>47.756164383561647</v>
       </c>
@@ -15326,16 +15329,16 @@
       <c r="M181" s="12">
         <v>27835617433</v>
       </c>
-      <c r="N181" s="36" t="s">
+      <c r="N181" s="35" t="s">
         <v>305</v>
       </c>
       <c r="O181" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P181" s="38" t="s">
+      <c r="P181" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="Q181" s="52" t="s">
+      <c r="Q181" s="51" t="s">
         <v>307</v>
       </c>
       <c r="R181" s="18" t="s">
@@ -15374,10 +15377,10 @@
       <c r="I182" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J182" s="59" t="s">
+      <c r="J182" s="5" t="s">
         <v>1105</v>
       </c>
-      <c r="K182" s="60">
+      <c r="K182" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>43.9972602739726</v>
       </c>
@@ -15387,16 +15390,16 @@
       <c r="M182" s="12">
         <v>28235653783</v>
       </c>
-      <c r="N182" s="36" t="s">
+      <c r="N182" s="35" t="s">
         <v>465</v>
       </c>
       <c r="O182" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P182" s="38" t="s">
+      <c r="P182" s="37" t="s">
         <v>466</v>
       </c>
-      <c r="Q182" s="52" t="s">
+      <c r="Q182" s="51" t="s">
         <v>467</v>
       </c>
       <c r="R182" s="18" t="s">
@@ -15435,10 +15438,10 @@
       <c r="I183" s="8" t="s">
         <v>1184</v>
       </c>
-      <c r="J183" s="59" t="s">
+      <c r="J183" s="5" t="s">
         <v>1106</v>
       </c>
-      <c r="K183" s="60">
+      <c r="K183" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>42.328767123287669</v>
       </c>
@@ -15448,16 +15451,16 @@
       <c r="M183" s="12">
         <v>28352455124</v>
       </c>
-      <c r="N183" s="36" t="s">
+      <c r="N183" s="35" t="s">
         <v>826</v>
       </c>
       <c r="O183" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P183" s="40" t="s">
+      <c r="P183" s="39" t="s">
         <v>827</v>
       </c>
-      <c r="Q183" s="39" t="s">
+      <c r="Q183" s="38" t="s">
         <v>828</v>
       </c>
       <c r="R183" s="18" t="s">
@@ -15495,10 +15498,10 @@
       <c r="I184" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J184" s="59" t="s">
+      <c r="J184" s="5" t="s">
         <v>1107</v>
       </c>
-      <c r="K184" s="60">
+      <c r="K184" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>51.652054794520545</v>
       </c>
@@ -15508,16 +15511,16 @@
       <c r="M184" s="12">
         <v>27414403823</v>
       </c>
-      <c r="N184" s="36" t="s">
+      <c r="N184" s="35" t="s">
         <v>528</v>
       </c>
       <c r="O184" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P184" s="38" t="s">
+      <c r="P184" s="37" t="s">
         <v>529</v>
       </c>
-      <c r="Q184" s="52" t="s">
+      <c r="Q184" s="51" t="s">
         <v>530</v>
       </c>
       <c r="R184" s="18" t="s">
@@ -15555,10 +15558,10 @@
       <c r="I185" s="8" t="s">
         <v>1262</v>
       </c>
-      <c r="J185" s="59" t="s">
+      <c r="J185" s="5" t="s">
         <v>1108</v>
       </c>
-      <c r="K185" s="60">
+      <c r="K185" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>47.295890410958904</v>
       </c>
@@ -15568,16 +15571,16 @@
       <c r="M185" s="18">
         <v>27814402287</v>
       </c>
-      <c r="N185" s="36" t="s">
+      <c r="N185" s="35" t="s">
         <v>859</v>
       </c>
       <c r="O185" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P185" s="40" t="s">
+      <c r="P185" s="39" t="s">
         <v>860</v>
       </c>
-      <c r="Q185" s="39" t="s">
+      <c r="Q185" s="38" t="s">
         <v>861</v>
       </c>
       <c r="R185" s="18" t="s">
@@ -15615,10 +15618,10 @@
       <c r="I186" s="8" t="s">
         <v>1263</v>
       </c>
-      <c r="J186" s="59" t="s">
+      <c r="J186" s="5" t="s">
         <v>1109</v>
       </c>
-      <c r="K186" s="60">
+      <c r="K186" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>52.084931506849315</v>
       </c>
@@ -15628,16 +15631,16 @@
       <c r="M186" s="12">
         <v>27414401781</v>
       </c>
-      <c r="N186" s="36" t="s">
+      <c r="N186" s="35" t="s">
         <v>172</v>
       </c>
       <c r="O186" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="P186" s="38" t="s">
+      <c r="P186" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="Q186" s="52" t="s">
+      <c r="Q186" s="51" t="s">
         <v>174</v>
       </c>
       <c r="R186" s="18" t="s">
@@ -15675,10 +15678,10 @@
       <c r="I187" s="8" t="s">
         <v>1201</v>
       </c>
-      <c r="J187" s="59" t="s">
+      <c r="J187" s="5" t="s">
         <v>1110</v>
       </c>
-      <c r="K187" s="60">
+      <c r="K187" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>56.101369863013701</v>
       </c>
@@ -15688,16 +15691,16 @@
       <c r="M187" s="12">
         <v>27076400444</v>
       </c>
-      <c r="N187" s="36" t="s">
+      <c r="N187" s="35" t="s">
         <v>695</v>
       </c>
-      <c r="O187" s="43" t="s">
+      <c r="O187" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P187" s="38" t="s">
+      <c r="P187" s="37" t="s">
         <v>696</v>
       </c>
-      <c r="Q187" s="52" t="s">
+      <c r="Q187" s="51" t="s">
         <v>697</v>
       </c>
       <c r="R187" s="18" t="s">
@@ -15735,10 +15738,10 @@
       <c r="I188" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J188" s="59" t="s">
+      <c r="J188" s="5" t="s">
         <v>1111</v>
       </c>
-      <c r="K188" s="60">
+      <c r="K188" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>50.865753424657534</v>
       </c>
@@ -15748,16 +15751,16 @@
       <c r="M188" s="12">
         <v>27576400269</v>
       </c>
-      <c r="N188" s="36" t="s">
+      <c r="N188" s="35" t="s">
         <v>496</v>
       </c>
       <c r="O188" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P188" s="38" t="s">
+      <c r="P188" s="37" t="s">
         <v>497</v>
       </c>
-      <c r="Q188" s="52" t="s">
+      <c r="Q188" s="51" t="s">
         <v>498</v>
       </c>
       <c r="R188" s="18" t="s">
@@ -15795,10 +15798,10 @@
       <c r="I189" s="8" t="s">
         <v>1264</v>
       </c>
-      <c r="J189" s="59" t="s">
+      <c r="J189" s="5" t="s">
         <v>1112</v>
       </c>
-      <c r="K189" s="60">
+      <c r="K189" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>44.726027397260275</v>
       </c>
@@ -15808,16 +15811,16 @@
       <c r="M189" s="12">
         <v>28135651157</v>
       </c>
-      <c r="N189" s="36" t="s">
+      <c r="N189" s="35" t="s">
         <v>287</v>
       </c>
-      <c r="O189" s="43" t="s">
+      <c r="O189" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P189" s="38" t="s">
+      <c r="P189" s="37" t="s">
         <v>288</v>
       </c>
-      <c r="Q189" s="52" t="s">
+      <c r="Q189" s="51" t="s">
         <v>289</v>
       </c>
       <c r="R189" s="18" t="s">
@@ -15855,10 +15858,10 @@
       <c r="I190" s="8" t="s">
         <v>1265</v>
       </c>
-      <c r="J190" s="59" t="s">
+      <c r="J190" s="5" t="s">
         <v>1113</v>
       </c>
-      <c r="K190" s="60">
+      <c r="K190" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>56.739726027397261</v>
       </c>
@@ -15868,16 +15871,16 @@
       <c r="M190" s="12">
         <v>26935629489</v>
       </c>
-      <c r="N190" s="36" t="s">
+      <c r="N190" s="35" t="s">
         <v>721</v>
       </c>
       <c r="O190" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P190" s="38" t="s">
+      <c r="P190" s="37" t="s">
         <v>722</v>
       </c>
-      <c r="Q190" s="52" t="s">
+      <c r="Q190" s="51" t="s">
         <v>723</v>
       </c>
       <c r="R190" s="18" t="s">
@@ -15915,10 +15918,10 @@
       <c r="I191" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J191" s="59" t="s">
+      <c r="J191" s="5" t="s">
         <v>1114</v>
       </c>
-      <c r="K191" s="60">
+      <c r="K191" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>34.506849315068493</v>
       </c>
@@ -15928,16 +15931,16 @@
       <c r="M191" s="12">
         <v>29135638686</v>
       </c>
-      <c r="N191" s="36" t="s">
+      <c r="N191" s="35" t="s">
         <v>476</v>
       </c>
       <c r="O191" s="16" t="s">
         <v>927</v>
       </c>
-      <c r="P191" s="38" t="s">
+      <c r="P191" s="37" t="s">
         <v>477</v>
       </c>
-      <c r="Q191" s="52" t="s">
+      <c r="Q191" s="51" t="s">
         <v>478</v>
       </c>
       <c r="R191" s="18" t="s">
@@ -15976,10 +15979,10 @@
       <c r="I192" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="J192" s="59" t="s">
+      <c r="J192" s="5" t="s">
         <v>1115</v>
       </c>
-      <c r="K192" s="60">
+      <c r="K192" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>62.410958904109592</v>
       </c>
@@ -15989,16 +15992,16 @@
       <c r="M192" s="12">
         <v>26376400558</v>
       </c>
-      <c r="N192" s="50" t="s">
+      <c r="N192" s="49" t="s">
         <v>32</v>
       </c>
       <c r="O192" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="P192" s="38" t="s">
+      <c r="P192" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="Q192" s="42" t="s">
+      <c r="Q192" s="41" t="s">
         <v>35</v>
       </c>
       <c r="R192" s="12" t="s">
@@ -16036,10 +16039,10 @@
       <c r="I193" s="8" t="s">
         <v>1267</v>
       </c>
-      <c r="J193" s="59" t="s">
+      <c r="J193" s="5" t="s">
         <v>1116</v>
       </c>
-      <c r="K193" s="60">
+      <c r="K193" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>49.030136986301372</v>
       </c>
@@ -16049,16 +16052,16 @@
       <c r="M193" s="12">
         <v>27735621851</v>
       </c>
-      <c r="N193" s="36" t="s">
+      <c r="N193" s="35" t="s">
         <v>214</v>
       </c>
       <c r="O193" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P193" s="38" t="s">
+      <c r="P193" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="Q193" s="52" t="s">
+      <c r="Q193" s="51" t="s">
         <v>216</v>
       </c>
       <c r="R193" s="18" t="s">
@@ -16097,10 +16100,10 @@
       <c r="I194" s="8" t="s">
         <v>1256</v>
       </c>
-      <c r="J194" s="59" t="s">
+      <c r="J194" s="5" t="s">
         <v>1117</v>
       </c>
-      <c r="K194" s="60">
+      <c r="K194" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>49.624657534246573</v>
       </c>
@@ -16110,16 +16113,16 @@
       <c r="M194" s="18">
         <v>27614400188</v>
       </c>
-      <c r="N194" s="36" t="s">
+      <c r="N194" s="35" t="s">
         <v>890</v>
       </c>
-      <c r="O194" s="43" t="s">
+      <c r="O194" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="P194" s="40" t="s">
+      <c r="P194" s="39" t="s">
         <v>891</v>
       </c>
-      <c r="Q194" s="39" t="s">
+      <c r="Q194" s="38" t="s">
         <v>892</v>
       </c>
       <c r="R194" s="18" t="s">
@@ -16157,10 +16160,10 @@
       <c r="I195" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="J195" s="59" t="s">
+      <c r="J195" s="5" t="s">
         <v>1118</v>
       </c>
-      <c r="K195" s="60">
+      <c r="K195" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>40.734246575342468</v>
       </c>
@@ -16170,16 +16173,16 @@
       <c r="M195" s="12">
         <v>28535609990</v>
       </c>
-      <c r="N195" s="36" t="s">
+      <c r="N195" s="35" t="s">
         <v>206</v>
       </c>
       <c r="O195" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P195" s="38" t="s">
+      <c r="P195" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="Q195" s="52" t="s">
+      <c r="Q195" s="51" t="s">
         <v>208</v>
       </c>
       <c r="R195" s="18" t="s">
@@ -16218,10 +16221,10 @@
       <c r="I196" s="8" t="s">
         <v>1269</v>
       </c>
-      <c r="J196" s="59" t="s">
+      <c r="J196" s="5" t="s">
         <v>1119</v>
       </c>
-      <c r="K196" s="60">
+      <c r="K196" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>44.520547945205479</v>
       </c>
@@ -16231,16 +16234,16 @@
       <c r="M196" s="12">
         <v>28135623543</v>
       </c>
-      <c r="N196" s="36" t="s">
+      <c r="N196" s="35" t="s">
         <v>746</v>
       </c>
       <c r="O196" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="P196" s="38" t="s">
+      <c r="P196" s="37" t="s">
         <v>747</v>
       </c>
-      <c r="Q196" s="52" t="s">
+      <c r="Q196" s="51" t="s">
         <v>748</v>
       </c>
       <c r="R196" s="18" t="s">
@@ -16279,10 +16282,10 @@
       <c r="I197" s="8" t="s">
         <v>1270</v>
       </c>
-      <c r="J197" s="59" t="s">
+      <c r="J197" s="5" t="s">
         <v>1120</v>
       </c>
-      <c r="K197" s="60">
+      <c r="K197" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>49.041095890410958</v>
       </c>
@@ -16292,16 +16295,16 @@
       <c r="M197" s="12">
         <v>27760806337</v>
       </c>
-      <c r="N197" s="36" t="s">
+      <c r="N197" s="35" t="s">
         <v>177</v>
       </c>
       <c r="O197" s="16" t="s">
         <v>927</v>
       </c>
-      <c r="P197" s="38" t="s">
+      <c r="P197" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="Q197" s="52" t="s">
+      <c r="Q197" s="51" t="s">
         <v>179</v>
       </c>
       <c r="R197" s="18" t="s">
@@ -16340,10 +16343,10 @@
       <c r="I198" s="8" t="s">
         <v>1182</v>
       </c>
-      <c r="J198" s="59" t="s">
+      <c r="J198" s="5" t="s">
         <v>1121</v>
       </c>
-      <c r="K198" s="60">
+      <c r="K198" s="58">
         <f t="shared" ref="K198:K200" ca="1" si="3">(TODAY()-(DATEVALUE(SUBSTITUTE(J198,".","/"))))/(365)</f>
         <v>44.654794520547945</v>
       </c>
@@ -16353,16 +16356,16 @@
       <c r="M198" s="12">
         <v>28114414463</v>
       </c>
-      <c r="N198" s="36" t="s">
+      <c r="N198" s="35" t="s">
         <v>685</v>
       </c>
       <c r="O198" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="P198" s="38" t="s">
+      <c r="P198" s="37" t="s">
         <v>686</v>
       </c>
-      <c r="Q198" s="52" t="s">
+      <c r="Q198" s="51" t="s">
         <v>687</v>
       </c>
       <c r="R198" s="18" t="s">
@@ -16401,10 +16404,10 @@
       <c r="I199" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="J199" s="59" t="s">
+      <c r="J199" s="5" t="s">
         <v>1122</v>
       </c>
-      <c r="K199" s="60">
+      <c r="K199" s="58">
         <f t="shared" ca="1" si="3"/>
         <v>57.230136986301368</v>
       </c>
@@ -16414,16 +16417,16 @@
       <c r="M199" s="12">
         <v>26852407572</v>
       </c>
-      <c r="N199" s="36" t="s">
+      <c r="N199" s="35" t="s">
         <v>457</v>
       </c>
       <c r="O199" s="16" t="s">
         <v>927</v>
       </c>
-      <c r="P199" s="38" t="s">
+      <c r="P199" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="Q199" s="52" t="s">
+      <c r="Q199" s="51" t="s">
         <v>459</v>
       </c>
       <c r="R199" s="18" t="s">
@@ -16462,10 +16465,10 @@
       <c r="I200" s="8" t="s">
         <v>1271</v>
       </c>
-      <c r="J200" s="59" t="s">
+      <c r="J200" s="5" t="s">
         <v>1123</v>
       </c>
-      <c r="K200" s="60">
+      <c r="K200" s="58">
         <f t="shared" ca="1" si="3"/>
         <v>38.284931506849318</v>
       </c>
@@ -16475,16 +16478,16 @@
       <c r="M200" s="12">
         <v>28752403232</v>
       </c>
-      <c r="N200" s="36" t="s">
+      <c r="N200" s="35" t="s">
         <v>335</v>
       </c>
       <c r="O200" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="P200" s="38" t="s">
+      <c r="P200" s="37" t="s">
         <v>336</v>
       </c>
-      <c r="Q200" s="52" t="s">
+      <c r="Q200" s="51" t="s">
         <v>337</v>
       </c>
       <c r="R200" s="18" t="s">
@@ -16504,15 +16507,15 @@
       <c r="F201" s="12"/>
       <c r="G201" s="12"/>
       <c r="H201" s="12"/>
-      <c r="I201" s="37"/>
-      <c r="J201" s="37"/>
-      <c r="K201" s="35"/>
+      <c r="I201" s="36"/>
+      <c r="J201" s="36"/>
+      <c r="K201" s="60"/>
       <c r="L201" s="18"/>
       <c r="M201" s="18"/>
-      <c r="N201" s="36"/>
+      <c r="N201" s="35"/>
       <c r="O201" s="16"/>
-      <c r="P201" s="40"/>
-      <c r="Q201" s="39"/>
+      <c r="P201" s="39"/>
+      <c r="Q201" s="38"/>
       <c r="R201" s="18"/>
       <c r="S201" s="18"/>
       <c r="T201" s="2"/>
@@ -16585,18 +16588,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
-    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CD0C5713D8B49840BA44FC47BC25FC9F" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d6c26ebffaa8bbd830e647f783d3198d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xmlns:ns3="40b16217-7e26-4dce-af97-68eaad0f1932" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f461dd4a85cef57f3309d1104a6214f5" ns2:_="" ns3:_="">
     <xsd:import namespace="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
@@ -16831,6 +16822,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
+    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14227109-D96A-4DED-A2D7-626D153602CC}">
   <ds:schemaRefs>
@@ -16840,17 +16843,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ADC4E22-EF51-4E34-B18F-C418F14AAB31}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
-    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3D938CC-FD3D-4613-B875-4FDEB235CAFD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16867,4 +16859,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ADC4E22-EF51-4E34-B18F-C418F14AAB31}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
+    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Emp_ List-Updated.xlsx
+++ b/Emp_ List-Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohamedShakeel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2170CC85-25B8-4EBF-A68B-C379E53D3A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2414A5EE-99A7-40E7-839B-1E3BB55156EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D210C182-0804-46D5-AC5E-017469378BAD}"/>
   </bookViews>
@@ -3863,8 +3863,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mmm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="00"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -4185,9 +4186,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4195,6 +4193,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4564,7 +4565,7 @@
     <col min="6" max="6" width="31.5703125" customWidth="1"/>
     <col min="7" max="8" width="8.5703125" customWidth="1"/>
     <col min="9" max="10" width="19" style="45" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" style="60" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="13.5703125" customWidth="1"/>
     <col min="14" max="14" width="15.42578125" customWidth="1"/>
     <col min="15" max="15" width="28.85546875" style="43" customWidth="1"/>
@@ -4607,7 +4608,7 @@
       <c r="J3" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="59" t="s">
+      <c r="K3" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -4667,7 +4668,7 @@
       <c r="J4" s="5" t="s">
         <v>930</v>
       </c>
-      <c r="K4" s="58">
+      <c r="K4" s="61">
         <f ca="1">(TODAY()-(DATEVALUE(SUBSTITUTE(J4,".","/"))))/(365)</f>
         <v>39.860273972602741</v>
       </c>
@@ -4728,7 +4729,7 @@
       <c r="J5" s="5" t="s">
         <v>931</v>
       </c>
-      <c r="K5" s="58">
+      <c r="K5" s="61">
         <f ca="1">(TODAY()-(DATEVALUE(SUBSTITUTE(J5,".","/"))))/(365)</f>
         <v>54.142465753424659</v>
       </c>
@@ -4789,7 +4790,7 @@
       <c r="J6" s="5" t="s">
         <v>932</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="61">
         <f t="shared" ref="K6:K69" ca="1" si="0">(TODAY()-(DATEVALUE(SUBSTITUTE(J6,".","/"))))/(365)</f>
         <v>53.747945205479454</v>
       </c>
@@ -4849,7 +4850,7 @@
       <c r="J7" s="5" t="s">
         <v>933</v>
       </c>
-      <c r="K7" s="58">
+      <c r="K7" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>33.315068493150683</v>
       </c>
@@ -4910,7 +4911,7 @@
       <c r="J8" s="5" t="s">
         <v>934</v>
       </c>
-      <c r="K8" s="58">
+      <c r="K8" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>49.586301369863016</v>
       </c>
@@ -4970,7 +4971,7 @@
       <c r="J9" s="5" t="s">
         <v>935</v>
       </c>
-      <c r="K9" s="58">
+      <c r="K9" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>40.273972602739725</v>
       </c>
@@ -5030,7 +5031,7 @@
       <c r="J10" s="5" t="s">
         <v>936</v>
       </c>
-      <c r="K10" s="58">
+      <c r="K10" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>62.975342465753428</v>
       </c>
@@ -5090,7 +5091,7 @@
       <c r="J11" s="5" t="s">
         <v>937</v>
       </c>
-      <c r="K11" s="58">
+      <c r="K11" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>30.172602739726027</v>
       </c>
@@ -5150,7 +5151,7 @@
       <c r="J12" s="5" t="s">
         <v>938</v>
       </c>
-      <c r="K12" s="58">
+      <c r="K12" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>28.898630136986302</v>
       </c>
@@ -5210,7 +5211,7 @@
       <c r="J13" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="K13" s="58">
+      <c r="K13" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>50.172602739726024</v>
       </c>
@@ -5270,7 +5271,7 @@
       <c r="J14" s="5" t="s">
         <v>940</v>
       </c>
-      <c r="K14" s="58">
+      <c r="K14" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>45.57260273972603</v>
       </c>
@@ -5330,7 +5331,7 @@
       <c r="J15" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="K15" s="58">
+      <c r="K15" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>61.835616438356162</v>
       </c>
@@ -5391,7 +5392,7 @@
       <c r="J16" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="K16" s="58">
+      <c r="K16" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>46.246575342465754</v>
       </c>
@@ -5451,7 +5452,7 @@
       <c r="J17" s="5" t="s">
         <v>943</v>
       </c>
-      <c r="K17" s="58">
+      <c r="K17" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>33.194520547945203</v>
       </c>
@@ -5511,7 +5512,7 @@
       <c r="J18" s="5" t="s">
         <v>944</v>
       </c>
-      <c r="K18" s="58">
+      <c r="K18" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>57.624657534246573</v>
       </c>
@@ -5571,7 +5572,7 @@
       <c r="J19" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="K19" s="58">
+      <c r="K19" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>41.164383561643838</v>
       </c>
@@ -5631,7 +5632,7 @@
       <c r="J20" s="5" t="s">
         <v>946</v>
       </c>
-      <c r="K20" s="58">
+      <c r="K20" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>32.104109589041094</v>
       </c>
@@ -5691,7 +5692,7 @@
       <c r="J21" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="K21" s="58">
+      <c r="K21" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>43.19178082191781</v>
       </c>
@@ -5751,7 +5752,7 @@
       <c r="J22" s="5" t="s">
         <v>948</v>
       </c>
-      <c r="K22" s="58">
+      <c r="K22" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>52.904109589041099</v>
       </c>
@@ -5811,7 +5812,7 @@
       <c r="J23" s="5" t="s">
         <v>949</v>
       </c>
-      <c r="K23" s="58">
+      <c r="K23" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>44.835616438356162</v>
       </c>
@@ -5871,7 +5872,7 @@
       <c r="J24" s="5" t="s">
         <v>950</v>
       </c>
-      <c r="K24" s="58">
+      <c r="K24" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>40.131506849315066</v>
       </c>
@@ -5931,7 +5932,7 @@
       <c r="J25" s="5" t="s">
         <v>951</v>
       </c>
-      <c r="K25" s="58">
+      <c r="K25" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>35.860273972602741</v>
       </c>
@@ -5992,7 +5993,7 @@
       <c r="J26" s="5" t="s">
         <v>952</v>
       </c>
-      <c r="K26" s="58">
+      <c r="K26" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>53.827397260273976</v>
       </c>
@@ -6052,7 +6053,7 @@
       <c r="J27" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="K27" s="58">
+      <c r="K27" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>30.731506849315068</v>
       </c>
@@ -6112,7 +6113,7 @@
       <c r="J28" s="5" t="s">
         <v>954</v>
       </c>
-      <c r="K28" s="58">
+      <c r="K28" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>34.857534246575341</v>
       </c>
@@ -6172,7 +6173,7 @@
       <c r="J29" s="5" t="s">
         <v>955</v>
       </c>
-      <c r="K29" s="58">
+      <c r="K29" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>59.865753424657534</v>
       </c>
@@ -6232,7 +6233,7 @@
       <c r="J30" s="5" t="s">
         <v>956</v>
       </c>
-      <c r="K30" s="58">
+      <c r="K30" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>24.687671232876713</v>
       </c>
@@ -6293,7 +6294,7 @@
       <c r="J31" s="5" t="s">
         <v>957</v>
       </c>
-      <c r="K31" s="58">
+      <c r="K31" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>49.07123287671233</v>
       </c>
@@ -6353,7 +6354,7 @@
       <c r="J32" s="5" t="s">
         <v>958</v>
       </c>
-      <c r="K32" s="58">
+      <c r="K32" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>43.846575342465755</v>
       </c>
@@ -6413,7 +6414,7 @@
       <c r="J33" s="5" t="s">
         <v>959</v>
       </c>
-      <c r="K33" s="58">
+      <c r="K33" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>40.838356164383562</v>
       </c>
@@ -6473,7 +6474,7 @@
       <c r="J34" s="5" t="s">
         <v>960</v>
       </c>
-      <c r="K34" s="58">
+      <c r="K34" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>39.38356164383562</v>
       </c>
@@ -6533,7 +6534,7 @@
       <c r="J35" s="5" t="s">
         <v>961</v>
       </c>
-      <c r="K35" s="58">
+      <c r="K35" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>45.994520547945207</v>
       </c>
@@ -6593,7 +6594,7 @@
       <c r="J36" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="K36" s="58">
+      <c r="K36" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>33.405479452054792</v>
       </c>
@@ -6654,7 +6655,7 @@
       <c r="J37" s="5" t="s">
         <v>963</v>
       </c>
-      <c r="K37" s="58">
+      <c r="K37" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>38.164383561643838</v>
       </c>
@@ -6714,7 +6715,7 @@
       <c r="J38" s="5" t="s">
         <v>964</v>
       </c>
-      <c r="K38" s="58">
+      <c r="K38" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>49.80821917808219</v>
       </c>
@@ -6774,7 +6775,7 @@
       <c r="J39" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="K39" s="58">
+      <c r="K39" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>40.753424657534246</v>
       </c>
@@ -6834,7 +6835,7 @@
       <c r="J40" s="5" t="s">
         <v>966</v>
       </c>
-      <c r="K40" s="58">
+      <c r="K40" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>45.421917808219177</v>
       </c>
@@ -6894,7 +6895,7 @@
       <c r="J41" s="5" t="s">
         <v>967</v>
       </c>
-      <c r="K41" s="58">
+      <c r="K41" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>45.098630136986301</v>
       </c>
@@ -6954,7 +6955,7 @@
       <c r="J42" s="5" t="s">
         <v>968</v>
       </c>
-      <c r="K42" s="58">
+      <c r="K42" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>47.81095890410959</v>
       </c>
@@ -7014,7 +7015,7 @@
       <c r="J43" s="5" t="s">
         <v>969</v>
       </c>
-      <c r="K43" s="58">
+      <c r="K43" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>46.849315068493148</v>
       </c>
@@ -7074,7 +7075,7 @@
       <c r="J44" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="K44" s="58">
+      <c r="K44" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>48.156164383561645</v>
       </c>
@@ -7134,7 +7135,7 @@
       <c r="J45" s="5" t="s">
         <v>971</v>
       </c>
-      <c r="K45" s="58">
+      <c r="K45" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>28.484931506849314</v>
       </c>
@@ -7194,7 +7195,7 @@
       <c r="J46" s="5" t="s">
         <v>972</v>
       </c>
-      <c r="K46" s="58">
+      <c r="K46" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>29.580821917808219</v>
       </c>
@@ -7254,7 +7255,7 @@
       <c r="J47" s="5" t="s">
         <v>973</v>
       </c>
-      <c r="K47" s="58">
+      <c r="K47" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>46.397260273972606</v>
       </c>
@@ -7314,7 +7315,7 @@
       <c r="J48" s="5" t="s">
         <v>974</v>
       </c>
-      <c r="K48" s="58">
+      <c r="K48" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>38.61917808219178</v>
       </c>
@@ -7374,7 +7375,7 @@
       <c r="J49" s="5" t="s">
         <v>975</v>
       </c>
-      <c r="K49" s="58">
+      <c r="K49" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>54.268493150684932</v>
       </c>
@@ -7434,7 +7435,7 @@
       <c r="J50" s="5" t="s">
         <v>976</v>
       </c>
-      <c r="K50" s="58">
+      <c r="K50" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>47.783561643835618</v>
       </c>
@@ -7495,7 +7496,7 @@
       <c r="J51" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="K51" s="58">
+      <c r="K51" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>46.909589041095892</v>
       </c>
@@ -7555,7 +7556,7 @@
       <c r="J52" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="K52" s="58">
+      <c r="K52" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>48.057534246575344</v>
       </c>
@@ -7615,7 +7616,7 @@
       <c r="J53" s="5" t="s">
         <v>979</v>
       </c>
-      <c r="K53" s="58">
+      <c r="K53" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>39.821917808219176</v>
       </c>
@@ -7675,7 +7676,7 @@
       <c r="J54" s="5" t="s">
         <v>980</v>
       </c>
-      <c r="K54" s="58">
+      <c r="K54" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>26.698630136986303</v>
       </c>
@@ -7735,7 +7736,7 @@
       <c r="J55" s="5" t="s">
         <v>981</v>
       </c>
-      <c r="K55" s="58">
+      <c r="K55" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>39.547945205479451</v>
       </c>
@@ -7795,7 +7796,7 @@
       <c r="J56" s="5" t="s">
         <v>982</v>
       </c>
-      <c r="K56" s="58">
+      <c r="K56" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>49.219178082191782</v>
       </c>
@@ -7855,7 +7856,7 @@
       <c r="J57" s="5" t="s">
         <v>983</v>
       </c>
-      <c r="K57" s="58">
+      <c r="K57" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>45.052054794520551</v>
       </c>
@@ -7915,7 +7916,7 @@
       <c r="J58" s="5" t="s">
         <v>984</v>
       </c>
-      <c r="K58" s="58">
+      <c r="K58" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>56.969863013698628</v>
       </c>
@@ -7975,7 +7976,7 @@
       <c r="J59" s="5" t="s">
         <v>985</v>
       </c>
-      <c r="K59" s="58">
+      <c r="K59" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>33.11780821917808</v>
       </c>
@@ -8035,7 +8036,7 @@
       <c r="J60" s="5" t="s">
         <v>986</v>
       </c>
-      <c r="K60" s="58">
+      <c r="K60" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>47.021917808219179</v>
       </c>
@@ -8095,7 +8096,7 @@
       <c r="J61" s="5" t="s">
         <v>987</v>
       </c>
-      <c r="K61" s="58">
+      <c r="K61" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>46.161643835616438</v>
       </c>
@@ -8155,7 +8156,7 @@
       <c r="J62" s="5" t="s">
         <v>988</v>
       </c>
-      <c r="K62" s="58">
+      <c r="K62" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>33.994520547945207</v>
       </c>
@@ -8215,7 +8216,7 @@
       <c r="J63" s="5" t="s">
         <v>989</v>
       </c>
-      <c r="K63" s="58">
+      <c r="K63" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>45.016438356164386</v>
       </c>
@@ -8275,7 +8276,7 @@
       <c r="J64" s="5" t="s">
         <v>990</v>
       </c>
-      <c r="K64" s="58">
+      <c r="K64" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>27.463013698630139</v>
       </c>
@@ -8335,7 +8336,7 @@
       <c r="J65" s="5" t="s">
         <v>991</v>
       </c>
-      <c r="K65" s="58">
+      <c r="K65" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>28.534246575342465</v>
       </c>
@@ -8396,7 +8397,7 @@
       <c r="J66" s="5" t="s">
         <v>992</v>
       </c>
-      <c r="K66" s="58">
+      <c r="K66" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>40.287671232876711</v>
       </c>
@@ -8457,7 +8458,7 @@
       <c r="J67" s="5" t="s">
         <v>993</v>
       </c>
-      <c r="K67" s="58">
+      <c r="K67" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>56.369863013698627</v>
       </c>
@@ -8517,7 +8518,7 @@
       <c r="J68" s="5" t="s">
         <v>994</v>
       </c>
-      <c r="K68" s="58">
+      <c r="K68" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>28.81095890410959</v>
       </c>
@@ -8578,7 +8579,7 @@
       <c r="J69" s="5" t="s">
         <v>995</v>
       </c>
-      <c r="K69" s="58">
+      <c r="K69" s="61">
         <f t="shared" ca="1" si="0"/>
         <v>39.750684931506846</v>
       </c>
@@ -8638,7 +8639,7 @@
       <c r="J70" s="5" t="s">
         <v>996</v>
       </c>
-      <c r="K70" s="58">
+      <c r="K70" s="61">
         <f t="shared" ref="K70:K133" ca="1" si="1">(TODAY()-(DATEVALUE(SUBSTITUTE(J70,".","/"))))/(365)</f>
         <v>32.526027397260272</v>
       </c>
@@ -8699,7 +8700,7 @@
       <c r="J71" s="5" t="s">
         <v>997</v>
       </c>
-      <c r="K71" s="58">
+      <c r="K71" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>49.2</v>
       </c>
@@ -8760,7 +8761,7 @@
       <c r="J72" s="5" t="s">
         <v>998</v>
       </c>
-      <c r="K72" s="58">
+      <c r="K72" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>41.273972602739725</v>
       </c>
@@ -8820,7 +8821,7 @@
       <c r="J73" s="5" t="s">
         <v>999</v>
       </c>
-      <c r="K73" s="58">
+      <c r="K73" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>47.07123287671233</v>
       </c>
@@ -8881,7 +8882,7 @@
       <c r="J74" s="5" t="s">
         <v>1000</v>
       </c>
-      <c r="K74" s="58">
+      <c r="K74" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>56.906849315068492</v>
       </c>
@@ -8941,7 +8942,7 @@
       <c r="J75" s="5" t="s">
         <v>1001</v>
       </c>
-      <c r="K75" s="58">
+      <c r="K75" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>35.520547945205479</v>
       </c>
@@ -9001,7 +9002,7 @@
       <c r="J76" s="5" t="s">
         <v>1002</v>
       </c>
-      <c r="K76" s="58">
+      <c r="K76" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>35.731506849315068</v>
       </c>
@@ -9061,7 +9062,7 @@
       <c r="J77" s="5" t="s">
         <v>1003</v>
       </c>
-      <c r="K77" s="58">
+      <c r="K77" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>52.739726027397261</v>
       </c>
@@ -9121,7 +9122,7 @@
       <c r="J78" s="5" t="s">
         <v>1004</v>
       </c>
-      <c r="K78" s="58">
+      <c r="K78" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>59.358904109589041</v>
       </c>
@@ -9181,7 +9182,7 @@
       <c r="J79" s="5" t="s">
         <v>1005</v>
       </c>
-      <c r="K79" s="58">
+      <c r="K79" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>40.364383561643834</v>
       </c>
@@ -9241,7 +9242,7 @@
       <c r="J80" s="5" t="s">
         <v>1006</v>
       </c>
-      <c r="K80" s="58">
+      <c r="K80" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>48.964383561643835</v>
       </c>
@@ -9301,7 +9302,7 @@
       <c r="J81" s="5" t="s">
         <v>1007</v>
       </c>
-      <c r="K81" s="58">
+      <c r="K81" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>55.627397260273973</v>
       </c>
@@ -9361,7 +9362,7 @@
       <c r="J82" s="5" t="s">
         <v>1008</v>
       </c>
-      <c r="K82" s="58">
+      <c r="K82" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>29.013698630136986</v>
       </c>
@@ -9421,7 +9422,7 @@
       <c r="J83" s="5" t="s">
         <v>1009</v>
       </c>
-      <c r="K83" s="58">
+      <c r="K83" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>52.81095890410959</v>
       </c>
@@ -9481,7 +9482,7 @@
       <c r="J84" s="5" t="s">
         <v>1010</v>
       </c>
-      <c r="K84" s="58">
+      <c r="K84" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>45.767123287671232</v>
       </c>
@@ -9541,7 +9542,7 @@
       <c r="J85" s="5" t="s">
         <v>1011</v>
       </c>
-      <c r="K85" s="58">
+      <c r="K85" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>60.145205479452052</v>
       </c>
@@ -9601,7 +9602,7 @@
       <c r="J86" s="5" t="s">
         <v>1012</v>
       </c>
-      <c r="K86" s="58">
+      <c r="K86" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>54.197260273972603</v>
       </c>
@@ -9661,7 +9662,7 @@
       <c r="J87" s="5" t="s">
         <v>1013</v>
       </c>
-      <c r="K87" s="58">
+      <c r="K87" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>40.953424657534249</v>
       </c>
@@ -9721,7 +9722,7 @@
       <c r="J88" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="K88" s="58">
+      <c r="K88" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>58.060273972602737</v>
       </c>
@@ -9781,7 +9782,7 @@
       <c r="J89" s="5" t="s">
         <v>1015</v>
       </c>
-      <c r="K89" s="58">
+      <c r="K89" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>44.895890410958906</v>
       </c>
@@ -9841,7 +9842,7 @@
       <c r="J90" s="5" t="s">
         <v>1016</v>
       </c>
-      <c r="K90" s="58">
+      <c r="K90" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>55.821917808219176</v>
       </c>
@@ -9901,7 +9902,7 @@
       <c r="J91" s="5" t="s">
         <v>1017</v>
       </c>
-      <c r="K91" s="58">
+      <c r="K91" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>33.545205479452058</v>
       </c>
@@ -9961,7 +9962,7 @@
       <c r="J92" s="5" t="s">
         <v>1018</v>
       </c>
-      <c r="K92" s="58">
+      <c r="K92" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>47.780821917808218</v>
       </c>
@@ -10021,7 +10022,7 @@
       <c r="J93" s="5" t="s">
         <v>1019</v>
       </c>
-      <c r="K93" s="58">
+      <c r="K93" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>43.219178082191782</v>
       </c>
@@ -10082,7 +10083,7 @@
       <c r="J94" s="5" t="s">
         <v>1020</v>
       </c>
-      <c r="K94" s="58">
+      <c r="K94" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>35.230136986301368</v>
       </c>
@@ -10142,7 +10143,7 @@
       <c r="J95" s="5" t="s">
         <v>1021</v>
       </c>
-      <c r="K95" s="58">
+      <c r="K95" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>42.794520547945204</v>
       </c>
@@ -10202,7 +10203,7 @@
       <c r="J96" s="5" t="s">
         <v>1022</v>
       </c>
-      <c r="K96" s="58">
+      <c r="K96" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>50.115068493150687</v>
       </c>
@@ -10262,7 +10263,7 @@
       <c r="J97" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="K97" s="58">
+      <c r="K97" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>43.657534246575345</v>
       </c>
@@ -10322,7 +10323,7 @@
       <c r="J98" s="5" t="s">
         <v>1024</v>
       </c>
-      <c r="K98" s="58">
+      <c r="K98" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>41.265753424657532</v>
       </c>
@@ -10382,7 +10383,7 @@
       <c r="J99" s="5" t="s">
         <v>1025</v>
       </c>
-      <c r="K99" s="58">
+      <c r="K99" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>39.983561643835614</v>
       </c>
@@ -10442,7 +10443,7 @@
       <c r="J100" s="5" t="s">
         <v>1026</v>
       </c>
-      <c r="K100" s="58">
+      <c r="K100" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>37.084931506849315</v>
       </c>
@@ -10502,7 +10503,7 @@
       <c r="J101" s="5" t="s">
         <v>1027</v>
       </c>
-      <c r="K101" s="58">
+      <c r="K101" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>58.419178082191777</v>
       </c>
@@ -10562,7 +10563,7 @@
       <c r="J102" s="5" t="s">
         <v>1028</v>
       </c>
-      <c r="K102" s="58">
+      <c r="K102" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>57.364383561643834</v>
       </c>
@@ -10622,7 +10623,7 @@
       <c r="J103" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="K103" s="58">
+      <c r="K103" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>37.802739726027397</v>
       </c>
@@ -10682,7 +10683,7 @@
       <c r="J104" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="K104" s="58">
+      <c r="K104" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>30.301369863013697</v>
       </c>
@@ -10742,7 +10743,7 @@
       <c r="J105" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="K105" s="58">
+      <c r="K105" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>50.660273972602738</v>
       </c>
@@ -10802,7 +10803,7 @@
       <c r="J106" s="5" t="s">
         <v>1032</v>
       </c>
-      <c r="K106" s="58">
+      <c r="K106" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>26.419178082191781</v>
       </c>
@@ -10862,7 +10863,7 @@
       <c r="J107" s="5" t="s">
         <v>1033</v>
       </c>
-      <c r="K107" s="58">
+      <c r="K107" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>43.128767123287673</v>
       </c>
@@ -10922,7 +10923,7 @@
       <c r="J108" s="5" t="s">
         <v>1034</v>
       </c>
-      <c r="K108" s="58">
+      <c r="K108" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>37.775342465753425</v>
       </c>
@@ -10982,7 +10983,7 @@
       <c r="J109" s="5" t="s">
         <v>1035</v>
       </c>
-      <c r="K109" s="58">
+      <c r="K109" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>38.739726027397261</v>
       </c>
@@ -11042,7 +11043,7 @@
       <c r="J110" s="5" t="s">
         <v>1036</v>
       </c>
-      <c r="K110" s="58">
+      <c r="K110" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>39.021917808219179</v>
       </c>
@@ -11102,7 +11103,7 @@
       <c r="J111" s="5" t="s">
         <v>1037</v>
       </c>
-      <c r="K111" s="58">
+      <c r="K111" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>46.531506849315072</v>
       </c>
@@ -11162,7 +11163,7 @@
       <c r="J112" s="5" t="s">
         <v>1038</v>
       </c>
-      <c r="K112" s="58">
+      <c r="K112" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>38.561643835616437</v>
       </c>
@@ -11222,7 +11223,7 @@
       <c r="J113" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="K113" s="58">
+      <c r="K113" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>46.016438356164386</v>
       </c>
@@ -11282,7 +11283,7 @@
       <c r="J114" s="5" t="s">
         <v>1040</v>
       </c>
-      <c r="K114" s="58">
+      <c r="K114" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>51.934246575342463</v>
       </c>
@@ -11342,7 +11343,7 @@
       <c r="J115" s="5" t="s">
         <v>1041</v>
       </c>
-      <c r="K115" s="58">
+      <c r="K115" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>36.668493150684931</v>
       </c>
@@ -11402,7 +11403,7 @@
       <c r="J116" s="5" t="s">
         <v>1042</v>
       </c>
-      <c r="K116" s="58">
+      <c r="K116" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>36.893150684931506</v>
       </c>
@@ -11462,7 +11463,7 @@
       <c r="J117" s="5" t="s">
         <v>1043</v>
       </c>
-      <c r="K117" s="58">
+      <c r="K117" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>27.473972602739725</v>
       </c>
@@ -11522,7 +11523,7 @@
       <c r="J118" s="5" t="s">
         <v>1044</v>
       </c>
-      <c r="K118" s="58">
+      <c r="K118" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>40.495890410958907</v>
       </c>
@@ -11582,7 +11583,7 @@
       <c r="J119" s="5" t="s">
         <v>1045</v>
       </c>
-      <c r="K119" s="58">
+      <c r="K119" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>41.169863013698631</v>
       </c>
@@ -11642,7 +11643,7 @@
       <c r="J120" s="5" t="s">
         <v>1046</v>
       </c>
-      <c r="K120" s="58">
+      <c r="K120" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>45.969863013698628</v>
       </c>
@@ -11702,7 +11703,7 @@
       <c r="J121" s="5" t="s">
         <v>1047</v>
       </c>
-      <c r="K121" s="58">
+      <c r="K121" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>38.290410958904111</v>
       </c>
@@ -11762,7 +11763,7 @@
       <c r="J122" s="5" t="s">
         <v>1048</v>
       </c>
-      <c r="K122" s="58">
+      <c r="K122" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>60.435616438356163</v>
       </c>
@@ -11822,7 +11823,7 @@
       <c r="J123" s="5" t="s">
         <v>1049</v>
       </c>
-      <c r="K123" s="58">
+      <c r="K123" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>38.016438356164386</v>
       </c>
@@ -11882,7 +11883,7 @@
       <c r="J124" s="5" t="s">
         <v>1050</v>
       </c>
-      <c r="K124" s="58">
+      <c r="K124" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>45.134246575342466</v>
       </c>
@@ -11942,7 +11943,7 @@
       <c r="J125" s="5" t="s">
         <v>1051</v>
       </c>
-      <c r="K125" s="58">
+      <c r="K125" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>40.764383561643832</v>
       </c>
@@ -12002,7 +12003,7 @@
       <c r="J126" s="5" t="s">
         <v>1052</v>
       </c>
-      <c r="K126" s="58">
+      <c r="K126" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>42.049315068493151</v>
       </c>
@@ -12062,7 +12063,7 @@
       <c r="J127" s="5" t="s">
         <v>1053</v>
       </c>
-      <c r="K127" s="58">
+      <c r="K127" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>31.295890410958904</v>
       </c>
@@ -12122,7 +12123,7 @@
       <c r="J128" s="5" t="s">
         <v>1054</v>
       </c>
-      <c r="K128" s="58">
+      <c r="K128" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>45.301369863013697</v>
       </c>
@@ -12182,7 +12183,7 @@
       <c r="J129" s="5" t="s">
         <v>1055</v>
       </c>
-      <c r="K129" s="58">
+      <c r="K129" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>42.838356164383562</v>
       </c>
@@ -12242,7 +12243,7 @@
       <c r="J130" s="5" t="s">
         <v>1056</v>
       </c>
-      <c r="K130" s="58">
+      <c r="K130" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>36</v>
       </c>
@@ -12302,7 +12303,7 @@
       <c r="J131" s="5" t="s">
         <v>1057</v>
       </c>
-      <c r="K131" s="58">
+      <c r="K131" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>42.56986301369863</v>
       </c>
@@ -12362,7 +12363,7 @@
       <c r="J132" s="5" t="s">
         <v>1058</v>
       </c>
-      <c r="K132" s="58">
+      <c r="K132" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>39.890410958904113</v>
       </c>
@@ -12422,7 +12423,7 @@
       <c r="J133" s="5" t="s">
         <v>1059</v>
       </c>
-      <c r="K133" s="58">
+      <c r="K133" s="61">
         <f t="shared" ca="1" si="1"/>
         <v>39.413698630136984</v>
       </c>
@@ -12482,7 +12483,7 @@
       <c r="J134" s="5" t="s">
         <v>1060</v>
       </c>
-      <c r="K134" s="58">
+      <c r="K134" s="61">
         <f t="shared" ref="K134:K197" ca="1" si="2">(TODAY()-(DATEVALUE(SUBSTITUTE(J134,".","/"))))/(365)</f>
         <v>41.81095890410959</v>
       </c>
@@ -12542,7 +12543,7 @@
       <c r="J135" s="5" t="s">
         <v>1061</v>
       </c>
-      <c r="K135" s="58">
+      <c r="K135" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>32.942465753424656</v>
       </c>
@@ -12602,7 +12603,7 @@
       <c r="J136" s="5" t="s">
         <v>1062</v>
       </c>
-      <c r="K136" s="58">
+      <c r="K136" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>41.364383561643834</v>
       </c>
@@ -12662,7 +12663,7 @@
       <c r="J137" s="5" t="s">
         <v>1063</v>
       </c>
-      <c r="K137" s="58">
+      <c r="K137" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>49.6</v>
       </c>
@@ -12722,7 +12723,7 @@
       <c r="J138" s="5" t="s">
         <v>1064</v>
       </c>
-      <c r="K138" s="58">
+      <c r="K138" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>41.38356164383562</v>
       </c>
@@ -12782,7 +12783,7 @@
       <c r="J139" s="5" t="s">
         <v>1065</v>
       </c>
-      <c r="K139" s="58">
+      <c r="K139" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>40.641095890410959</v>
       </c>
@@ -12842,7 +12843,7 @@
       <c r="J140" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="K140" s="58">
+      <c r="K140" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>46.016438356164386</v>
       </c>
@@ -12902,7 +12903,7 @@
       <c r="J141" s="5" t="s">
         <v>1066</v>
       </c>
-      <c r="K141" s="58">
+      <c r="K141" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>40.958904109589042</v>
       </c>
@@ -12962,7 +12963,7 @@
       <c r="J142" s="5" t="s">
         <v>1067</v>
       </c>
-      <c r="K142" s="58">
+      <c r="K142" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>40.775342465753425</v>
       </c>
@@ -13022,7 +13023,7 @@
       <c r="J143" s="5" t="s">
         <v>1068</v>
       </c>
-      <c r="K143" s="58">
+      <c r="K143" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>40.698630136986303</v>
       </c>
@@ -13082,7 +13083,7 @@
       <c r="J144" s="5" t="s">
         <v>1069</v>
       </c>
-      <c r="K144" s="58">
+      <c r="K144" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>43.591780821917808</v>
       </c>
@@ -13142,7 +13143,7 @@
       <c r="J145" s="5" t="s">
         <v>1070</v>
       </c>
-      <c r="K145" s="58">
+      <c r="K145" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>48.101369863013701</v>
       </c>
@@ -13203,7 +13204,7 @@
       <c r="J146" s="5" t="s">
         <v>1071</v>
       </c>
-      <c r="K146" s="58">
+      <c r="K146" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>40.545205479452058</v>
       </c>
@@ -13263,7 +13264,7 @@
       <c r="J147" s="5" t="s">
         <v>1072</v>
       </c>
-      <c r="K147" s="58">
+      <c r="K147" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>41.446575342465756</v>
       </c>
@@ -13323,7 +13324,7 @@
       <c r="J148" s="5" t="s">
         <v>1073</v>
       </c>
-      <c r="K148" s="58">
+      <c r="K148" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>48.92876712328767</v>
       </c>
@@ -13383,7 +13384,7 @@
       <c r="J149" s="5" t="s">
         <v>1074</v>
       </c>
-      <c r="K149" s="58">
+      <c r="K149" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>54.780821917808218</v>
       </c>
@@ -13443,7 +13444,7 @@
       <c r="J150" s="5" t="s">
         <v>1075</v>
       </c>
-      <c r="K150" s="58">
+      <c r="K150" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>39.753424657534246</v>
       </c>
@@ -13503,7 +13504,7 @@
       <c r="J151" s="5" t="s">
         <v>1076</v>
       </c>
-      <c r="K151" s="58">
+      <c r="K151" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>39.243835616438353</v>
       </c>
@@ -13563,7 +13564,7 @@
       <c r="J152" s="5" t="s">
         <v>1077</v>
       </c>
-      <c r="K152" s="58">
+      <c r="K152" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>33.493150684931507</v>
       </c>
@@ -13623,7 +13624,7 @@
       <c r="J153" s="5" t="s">
         <v>1078</v>
       </c>
-      <c r="K153" s="58">
+      <c r="K153" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>47.991780821917807</v>
       </c>
@@ -13683,7 +13684,7 @@
       <c r="J154" s="5" t="s">
         <v>1079</v>
       </c>
-      <c r="K154" s="58">
+      <c r="K154" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>45.07123287671233</v>
       </c>
@@ -13743,7 +13744,7 @@
       <c r="J155" s="5" t="s">
         <v>1080</v>
       </c>
-      <c r="K155" s="58">
+      <c r="K155" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>36.12054794520548</v>
       </c>
@@ -13803,7 +13804,7 @@
       <c r="J156" s="5" t="s">
         <v>1081</v>
       </c>
-      <c r="K156" s="58">
+      <c r="K156" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>44.328767123287669</v>
       </c>
@@ -13863,7 +13864,7 @@
       <c r="J157" s="5" t="s">
         <v>1082</v>
       </c>
-      <c r="K157" s="58">
+      <c r="K157" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>45.906849315068492</v>
       </c>
@@ -13923,7 +13924,7 @@
       <c r="J158" s="5" t="s">
         <v>1083</v>
       </c>
-      <c r="K158" s="58">
+      <c r="K158" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>36.526027397260272</v>
       </c>
@@ -13984,7 +13985,7 @@
       <c r="J159" s="5" t="s">
         <v>1084</v>
       </c>
-      <c r="K159" s="58">
+      <c r="K159" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>42.276712328767125</v>
       </c>
@@ -14044,7 +14045,7 @@
       <c r="J160" s="5" t="s">
         <v>1085</v>
       </c>
-      <c r="K160" s="58">
+      <c r="K160" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>53.753424657534246</v>
       </c>
@@ -14104,7 +14105,7 @@
       <c r="J161" s="5" t="s">
         <v>1086</v>
       </c>
-      <c r="K161" s="58">
+      <c r="K161" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>38.446575342465756</v>
       </c>
@@ -14164,7 +14165,7 @@
       <c r="J162" s="5" t="s">
         <v>1087</v>
       </c>
-      <c r="K162" s="58">
+      <c r="K162" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>53.939726027397263</v>
       </c>
@@ -14224,7 +14225,7 @@
       <c r="J163" s="5" t="s">
         <v>1088</v>
       </c>
-      <c r="K163" s="58">
+      <c r="K163" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>60.452054794520549</v>
       </c>
@@ -14284,7 +14285,7 @@
       <c r="J164" s="5" t="s">
         <v>1089</v>
       </c>
-      <c r="K164" s="58">
+      <c r="K164" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>45.194520547945203</v>
       </c>
@@ -14345,7 +14346,7 @@
       <c r="J165" s="5" t="s">
         <v>1090</v>
       </c>
-      <c r="K165" s="58">
+      <c r="K165" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>36.701369863013696</v>
       </c>
@@ -14406,7 +14407,7 @@
       <c r="J166" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="K166" s="58">
+      <c r="K166" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>45.780821917808218</v>
       </c>
@@ -14467,7 +14468,7 @@
       <c r="J167" s="5" t="s">
         <v>931</v>
       </c>
-      <c r="K167" s="58">
+      <c r="K167" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>54.142465753424659</v>
       </c>
@@ -14528,7 +14529,7 @@
       <c r="J168" s="5" t="s">
         <v>1092</v>
       </c>
-      <c r="K168" s="58">
+      <c r="K168" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>41.679452054794524</v>
       </c>
@@ -14589,7 +14590,7 @@
       <c r="J169" s="5" t="s">
         <v>1093</v>
       </c>
-      <c r="K169" s="58">
+      <c r="K169" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>34.084931506849315</v>
       </c>
@@ -14650,7 +14651,7 @@
       <c r="J170" s="5" t="s">
         <v>1094</v>
       </c>
-      <c r="K170" s="58">
+      <c r="K170" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>27.742465753424657</v>
       </c>
@@ -14711,7 +14712,7 @@
       <c r="J171" s="5" t="s">
         <v>1095</v>
       </c>
-      <c r="K171" s="58">
+      <c r="K171" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>36.643835616438359</v>
       </c>
@@ -14772,7 +14773,7 @@
       <c r="J172" s="5" t="s">
         <v>1096</v>
       </c>
-      <c r="K172" s="58">
+      <c r="K172" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>50.238356164383561</v>
       </c>
@@ -14833,7 +14834,7 @@
       <c r="J173" s="5" t="s">
         <v>1097</v>
       </c>
-      <c r="K173" s="58">
+      <c r="K173" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>51.701369863013696</v>
       </c>
@@ -14894,7 +14895,7 @@
       <c r="J174" s="5" t="s">
         <v>1098</v>
       </c>
-      <c r="K174" s="58">
+      <c r="K174" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>30.756164383561643</v>
       </c>
@@ -14954,7 +14955,7 @@
       <c r="J175" s="5" t="s">
         <v>1099</v>
       </c>
-      <c r="K175" s="58">
+      <c r="K175" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>41.397260273972606</v>
       </c>
@@ -15014,7 +15015,7 @@
       <c r="J176" s="5" t="s">
         <v>1100</v>
       </c>
-      <c r="K176" s="58">
+      <c r="K176" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>33.457534246575342</v>
       </c>
@@ -15075,7 +15076,7 @@
       <c r="J177" s="5" t="s">
         <v>1101</v>
       </c>
-      <c r="K177" s="58">
+      <c r="K177" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>43.720547945205482</v>
       </c>
@@ -15136,7 +15137,7 @@
       <c r="J178" s="5" t="s">
         <v>1102</v>
       </c>
-      <c r="K178" s="58">
+      <c r="K178" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>45.630136986301373</v>
       </c>
@@ -15197,7 +15198,7 @@
       <c r="J179" s="5" t="s">
         <v>1103</v>
       </c>
-      <c r="K179" s="58">
+      <c r="K179" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>34.69041095890411</v>
       </c>
@@ -15258,7 +15259,7 @@
       <c r="J180" s="5" t="s">
         <v>930</v>
       </c>
-      <c r="K180" s="58">
+      <c r="K180" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>39.860273972602741</v>
       </c>
@@ -15319,7 +15320,7 @@
       <c r="J181" s="5" t="s">
         <v>1104</v>
       </c>
-      <c r="K181" s="58">
+      <c r="K181" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>47.756164383561647</v>
       </c>
@@ -15380,7 +15381,7 @@
       <c r="J182" s="5" t="s">
         <v>1105</v>
       </c>
-      <c r="K182" s="58">
+      <c r="K182" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>43.9972602739726</v>
       </c>
@@ -15441,7 +15442,7 @@
       <c r="J183" s="5" t="s">
         <v>1106</v>
       </c>
-      <c r="K183" s="58">
+      <c r="K183" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>42.328767123287669</v>
       </c>
@@ -15501,7 +15502,7 @@
       <c r="J184" s="5" t="s">
         <v>1107</v>
       </c>
-      <c r="K184" s="58">
+      <c r="K184" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>51.652054794520545</v>
       </c>
@@ -15561,7 +15562,7 @@
       <c r="J185" s="5" t="s">
         <v>1108</v>
       </c>
-      <c r="K185" s="58">
+      <c r="K185" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>47.295890410958904</v>
       </c>
@@ -15621,7 +15622,7 @@
       <c r="J186" s="5" t="s">
         <v>1109</v>
       </c>
-      <c r="K186" s="58">
+      <c r="K186" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>52.084931506849315</v>
       </c>
@@ -15681,7 +15682,7 @@
       <c r="J187" s="5" t="s">
         <v>1110</v>
       </c>
-      <c r="K187" s="58">
+      <c r="K187" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>56.101369863013701</v>
       </c>
@@ -15741,7 +15742,7 @@
       <c r="J188" s="5" t="s">
         <v>1111</v>
       </c>
-      <c r="K188" s="58">
+      <c r="K188" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>50.865753424657534</v>
       </c>
@@ -15801,7 +15802,7 @@
       <c r="J189" s="5" t="s">
         <v>1112</v>
       </c>
-      <c r="K189" s="58">
+      <c r="K189" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>44.726027397260275</v>
       </c>
@@ -15861,7 +15862,7 @@
       <c r="J190" s="5" t="s">
         <v>1113</v>
       </c>
-      <c r="K190" s="58">
+      <c r="K190" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>56.739726027397261</v>
       </c>
@@ -15921,7 +15922,7 @@
       <c r="J191" s="5" t="s">
         <v>1114</v>
       </c>
-      <c r="K191" s="58">
+      <c r="K191" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>34.506849315068493</v>
       </c>
@@ -15982,7 +15983,7 @@
       <c r="J192" s="5" t="s">
         <v>1115</v>
       </c>
-      <c r="K192" s="58">
+      <c r="K192" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>62.410958904109592</v>
       </c>
@@ -16042,7 +16043,7 @@
       <c r="J193" s="5" t="s">
         <v>1116</v>
       </c>
-      <c r="K193" s="58">
+      <c r="K193" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>49.030136986301372</v>
       </c>
@@ -16103,7 +16104,7 @@
       <c r="J194" s="5" t="s">
         <v>1117</v>
       </c>
-      <c r="K194" s="58">
+      <c r="K194" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>49.624657534246573</v>
       </c>
@@ -16163,7 +16164,7 @@
       <c r="J195" s="5" t="s">
         <v>1118</v>
       </c>
-      <c r="K195" s="58">
+      <c r="K195" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>40.734246575342468</v>
       </c>
@@ -16224,7 +16225,7 @@
       <c r="J196" s="5" t="s">
         <v>1119</v>
       </c>
-      <c r="K196" s="58">
+      <c r="K196" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>44.520547945205479</v>
       </c>
@@ -16285,7 +16286,7 @@
       <c r="J197" s="5" t="s">
         <v>1120</v>
       </c>
-      <c r="K197" s="58">
+      <c r="K197" s="61">
         <f t="shared" ca="1" si="2"/>
         <v>49.041095890410958</v>
       </c>
@@ -16346,7 +16347,7 @@
       <c r="J198" s="5" t="s">
         <v>1121</v>
       </c>
-      <c r="K198" s="58">
+      <c r="K198" s="61">
         <f t="shared" ref="K198:K200" ca="1" si="3">(TODAY()-(DATEVALUE(SUBSTITUTE(J198,".","/"))))/(365)</f>
         <v>44.654794520547945</v>
       </c>
@@ -16407,7 +16408,7 @@
       <c r="J199" s="5" t="s">
         <v>1122</v>
       </c>
-      <c r="K199" s="58">
+      <c r="K199" s="61">
         <f t="shared" ca="1" si="3"/>
         <v>57.230136986301368</v>
       </c>
@@ -16468,7 +16469,7 @@
       <c r="J200" s="5" t="s">
         <v>1123</v>
       </c>
-      <c r="K200" s="58">
+      <c r="K200" s="61">
         <f t="shared" ca="1" si="3"/>
         <v>38.284931506849318</v>
       </c>
@@ -16509,7 +16510,7 @@
       <c r="H201" s="12"/>
       <c r="I201" s="36"/>
       <c r="J201" s="36"/>
-      <c r="K201" s="60"/>
+      <c r="K201" s="59"/>
       <c r="L201" s="18"/>
       <c r="M201" s="18"/>
       <c r="N201" s="35"/>
@@ -16579,12 +16580,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
+    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16823,21 +16827,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
-    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14227109-D96A-4DED-A2D7-626D153602CC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ADC4E22-EF51-4E34-B18F-C418F14AAB31}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
+    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16862,12 +16866,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ADC4E22-EF51-4E34-B18F-C418F14AAB31}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14227109-D96A-4DED-A2D7-626D153602CC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
-    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>